--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Гребёнка (коллектор) Ду 32 на 7 выходов с шаровыми кранами на выходах, латунь никелированная</t>
+          <t>Гребёнка (коллектор) Ду 32 на 8 выходов с шаровыми кранами на выходах, латунь никелированная</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1068,7 +1068,7 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>КХ, топочная 1.6</t>
+          <t>КХ, топочная 1.6; КХ-8 — автополив</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 37,9, Т3 7,9 м + 10 %</t>
+          <t>по модели В1 41,8, Т3 7,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø110×2,7</t>
+          <t>Труба канализационная малошумная трёхслойная Ø110 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr"/>
@@ -1543,12 +1543,12 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>внутри здания; по модели 24,9 м</t>
+          <t>2 этаж, короб гаража, Ст.К1-1; по модели 17,1 м</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø50×1,8</t>
+          <t>Труба канализационная малошумная трёхслойная Ø50 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>внутри здания; по модели 20,5 м</t>
+          <t>2 этаж, короб гаража, Ст.К1-1; по модели 10,4 м</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
+          <t>Труба канализационная малошумная трёхслойная Ø32 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr"/>
@@ -1605,12 +1605,12 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 21,1 м</t>
+          <t>2 этаж, короб гаража, Ст.К1-1; по модели 0,6 м</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32×1,8</t>
+          <t>Труба полипропиленовая канализационная Ø110×2,7</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1636,12 +1636,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>внутри здания; по модели 0,6 м</t>
+          <t>баня, подъёмы к приборам 1 этажа; по модели 7,8 м</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
+          <t>Труба полипропиленовая канализационная Ø50×1,8</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr"/>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 31,3 м + стояки прочисток 2 × 0,8 м</t>
+          <t>баня, подъёмы к приборам 1 этажа; по модели 10,1 м</t>
         </is>
       </c>
     </row>
@@ -1682,58 +1682,74 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
+          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr"/>
       <c r="E43" s="1" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>выпуски К1-1, К1-б (лист 14, узел 2)</t>
+          <t>отводы в песчаной обсыпке; по модели 21,1 м</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="n"/>
-      <c r="D44" s="1" t="n"/>
-      <c r="E44" s="1" t="n"/>
-      <c r="F44" s="1" t="n"/>
-      <c r="G44" s="1" t="n"/>
-      <c r="H44" s="1" t="n"/>
-      <c r="I44" s="1" t="n"/>
+      <c r="A44" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32413-2013</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr"/>
+      <c r="E44" s="1" t="inlineStr"/>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="H44" s="1" t="inlineStr"/>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>сборные под плитой и выпуски; по модели 31,3 м + стояки прочисток 2 × 0,8 м</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
+          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr"/>
@@ -1744,45 +1760,29 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>выходы коллекторов</t>
+          <t>выпуски К1-1, К1-б (лист 14, узел 2)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>выходы коллекторов</t>
-        </is>
-      </c>
+      <c r="A46" s="1" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n"/>
+      <c r="D46" s="1" t="n"/>
+      <c r="E46" s="1" t="n"/>
+      <c r="F46" s="1" t="n"/>
+      <c r="G46" s="1" t="n"/>
+      <c r="H46" s="1" t="n"/>
+      <c r="I46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1837,12 +1837,12 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1868,12 +1868,12 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1930,12 +1930,12 @@
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
+          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1961,12 +1961,12 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1992,12 +1992,12 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2023,12 +2023,12 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2116,12 +2116,12 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>в приямке ввода (лист 14, узел 1)</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2143,7 +2143,7 @@
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G58" s="1" t="n">
@@ -2152,7 +2152,7 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr"/>
@@ -2178,12 +2178,12 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели, прочистки</t>
+          <t>в приямке ввода (лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2193,28 +2193,28 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr"/>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø32, 45°</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr"/>
@@ -2271,12 +2271,12 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
@@ -2302,12 +2302,12 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×32</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
@@ -2395,12 +2395,12 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>К1-1 у 1.8, К1-б у б2</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Ревизия ПП канализационная Ø110</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2426,12 +2426,12 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), начало сборного в гараже</t>
+          <t>повороты по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2457,12 +2457,12 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2484,46 +2484,62 @@
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr"/>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 39 шт.)</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="n"/>
-      <c r="D70" s="1" t="n"/>
-      <c r="E70" s="1" t="n"/>
-      <c r="F70" s="1" t="n"/>
-      <c r="G70" s="1" t="n"/>
-      <c r="H70" s="1" t="n"/>
-      <c r="I70" s="1" t="n"/>
+      <c r="A70" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr"/>
+      <c r="E70" s="1" t="inlineStr"/>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="1" t="inlineStr"/>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>присоединения по модели</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
@@ -2539,22 +2555,22 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
+          <t>К1-1 у 1.8, К1-б у б2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
@@ -2565,27 +2581,27 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
+          <t>Ст.К1-1 (+1,000), начало сборного в гараже</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
@@ -2601,71 +2617,55 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>прочистки в грунте</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr"/>
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>выход Т4 из ШВК-1 и ШВК-Б (П4)</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Кран поливочный незамерзающий Ду 15 с выносом через стену</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t>ПК-1…ПК-3</t>
-        </is>
-      </c>
+      <c r="A75" s="1" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 40 шт.)</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n"/>
+      <c r="D75" s="1" t="n"/>
+      <c r="E75" s="1" t="n"/>
+      <c r="F75" s="1" t="n"/>
+      <c r="G75" s="1" t="n"/>
+      <c r="H75" s="1" t="n"/>
+      <c r="I75" s="1" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2689,12 +2689,12 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2720,197 +2720,213 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
+          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr"/>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="n"/>
-      <c r="D78" s="1" t="n"/>
-      <c r="E78" s="1" t="n"/>
-      <c r="F78" s="1" t="n"/>
-      <c r="G78" s="1" t="n"/>
-      <c r="H78" s="1" t="n"/>
-      <c r="I78" s="1" t="n"/>
+      <c r="A78" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Клапан обратный Ду 15 (Т4)</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr"/>
+      <c r="E78" s="1" t="inlineStr"/>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>на Т4 у Н8, Н9</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr"/>
       <c r="E79" s="1" t="inlineStr"/>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr"/>
       <c r="E80" s="1" t="inlineStr"/>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-3, УМ-б1</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr"/>
       <c r="E81" s="1" t="inlineStr"/>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr"/>
       <c r="E82" s="1" t="inlineStr"/>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>выход Т4 из ШВК-1 и ШВК-Б (П4)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Кран поливочный незамерзающий Ду 15 с выносом через стену</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr"/>
       <c r="E83" s="1" t="inlineStr"/>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>ПК-1…ПК-3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr"/>
@@ -2926,17 +2942,17 @@
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2952,45 +2968,29 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
-          <t>Т-1 (топочная)</t>
-        </is>
-      </c>
+      <c r="A86" s="1" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n"/>
+      <c r="D86" s="1" t="n"/>
+      <c r="E86" s="1" t="n"/>
+      <c r="F86" s="1" t="n"/>
+      <c r="G86" s="1" t="n"/>
+      <c r="H86" s="1" t="n"/>
+      <c r="I86" s="1" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -2998,28 +2998,28 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr"/>
       <c r="E87" s="1" t="inlineStr"/>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3029,28 +3029,28 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr"/>
       <c r="E88" s="1" t="inlineStr"/>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>УМ-1…УМ-3, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3060,28 +3060,28 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr"/>
       <c r="E89" s="1" t="inlineStr"/>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3091,28 +3091,28 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr"/>
       <c r="E90" s="1" t="inlineStr"/>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3122,19 +3122,19 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr"/>
       <c r="E91" s="1" t="inlineStr"/>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G91" s="1" t="n">
@@ -3143,7 +3143,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный напольный 300×300 мм под плитку, герметичный</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr"/>
@@ -3169,37 +3169,53 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>1.8, б2 (узел 5)</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>7. Изоляция, гильзы и крепления</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="n"/>
-      <c r="D93" s="1" t="n"/>
-      <c r="E93" s="1" t="n"/>
-      <c r="F93" s="1" t="n"/>
-      <c r="G93" s="1" t="n"/>
-      <c r="H93" s="1" t="n"/>
-      <c r="I93" s="1" t="n"/>
+      <c r="A93" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr"/>
+      <c r="E93" s="1" t="inlineStr"/>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" s="1" t="inlineStr"/>
+      <c r="I93" s="1" t="inlineStr">
+        <is>
+          <t>Д-3, Д-б1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3211,26 +3227,26 @@
       <c r="E94" s="1" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G94" s="1" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3242,26 +3258,26 @@
       <c r="E95" s="1" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3273,26 +3289,26 @@
       <c r="E96" s="1" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3304,26 +3320,26 @@
       <c r="E97" s="1" t="inlineStr"/>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3335,57 +3351,57 @@
       <c r="E98" s="1" t="inlineStr"/>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr"/>
       <c r="E99" s="1" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Люк ревизионный напольный 300×300 мм под плитку, герметичный</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -3397,49 +3413,33 @@
       <c r="E100" s="1" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>1.8, б2 (узел 5)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr"/>
-      <c r="E101" s="1" t="inlineStr"/>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H101" s="1" t="inlineStr"/>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>в проёме фундамента</t>
-        </is>
-      </c>
+      <c r="A101" s="1" t="inlineStr"/>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>7. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n"/>
+      <c r="D101" s="1" t="n"/>
+      <c r="E101" s="1" t="n"/>
+      <c r="F101" s="1" t="n"/>
+      <c r="G101" s="1" t="n"/>
+      <c r="H101" s="1" t="n"/>
+      <c r="I101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3463,12 +3463,12 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -3494,12 +3494,12 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3509,28 +3509,28 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr"/>
       <c r="E104" s="1" t="inlineStr"/>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 7, стены 4 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3540,28 +3540,28 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr"/>
       <c r="E105" s="1" t="inlineStr"/>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 25, стены 10 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3571,28 +3571,28 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr"/>
       <c r="E106" s="1" t="inlineStr"/>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 13, стены 0 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3614,16 +3614,16 @@
       <c r="E107" s="1" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3645,16 +3645,16 @@
       <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>ввод В1, выпуски К1-1, К1-б (п. 8.8)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3676,16 +3676,16 @@
       <c r="E109" s="1" t="inlineStr"/>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>в проёме фундамента</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3707,16 +3707,16 @@
       <c r="E110" s="1" t="inlineStr"/>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3738,16 +3738,16 @@
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3757,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
@@ -3773,12 +3773,12 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>перекрытия и плиты 7, стены 4 (лист 14)</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr"/>
@@ -3804,12 +3804,12 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>перекрытия и плиты 25, стены 10 (лист 14)</t>
         </is>
       </c>
     </row>
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr"/>
@@ -3835,12 +3835,12 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>перекрытия и плиты 13, стены 0 (лист 14)</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3862,16 +3862,16 @@
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Заделка проёмов фундамента: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3893,105 +3893,370 @@
       <c r="E116" s="1" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>450</v>
+        <v>3</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>шаг 0,5 м</t>
+          <t>ввод В1 и подводка автополива (общий проём), выпуски К1-1, К1-б (п. 8.8)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="inlineStr"/>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>8. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="n"/>
-      <c r="D117" s="1" t="n"/>
-      <c r="E117" s="1" t="n"/>
-      <c r="F117" s="1" t="n"/>
-      <c r="G117" s="1" t="n"/>
-      <c r="H117" s="1" t="n"/>
-      <c r="I117" s="1" t="n"/>
+      <c r="A117" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr"/>
+      <c r="E117" s="1" t="inlineStr"/>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="H117" s="1" t="inlineStr"/>
+      <c r="I117" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D118" s="1" t="inlineStr"/>
       <c r="E118" s="1" t="inlineStr"/>
-      <c r="F118" s="1" t="inlineStr"/>
-      <c r="G118" s="1" t="inlineStr"/>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="n">
+        <v>133</v>
+      </c>
       <c r="H118" s="1" t="inlineStr"/>
-      <c r="I118" s="1" t="inlineStr"/>
+      <c r="I118" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D119" s="1" t="inlineStr"/>
       <c r="E119" s="1" t="inlineStr"/>
-      <c r="F119" s="1" t="inlineStr"/>
-      <c r="G119" s="1" t="inlineStr"/>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>43</v>
+      </c>
       <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr"/>
+      <c r="I119" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, колодцы, водоподготовка (при скважине) — раздел НВК</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D120" s="1" t="inlineStr"/>
       <c r="E120" s="1" t="inlineStr"/>
-      <c r="F120" s="1" t="inlineStr"/>
-      <c r="G120" s="1" t="inlineStr"/>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr"/>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Короба, люки 600×600 и 300×400 в коробах, ниши — по АР (ТЗ-1)</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D121" s="1" t="inlineStr"/>
       <c r="E121" s="1" t="inlineStr"/>
-      <c r="F121" s="1" t="inlineStr"/>
-      <c r="G121" s="1" t="inlineStr"/>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G121" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="H121" s="1" t="inlineStr"/>
-      <c r="I121" s="1" t="inlineStr"/>
+      <c r="I121" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr"/>
+      <c r="E122" s="1" t="inlineStr"/>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" s="1" t="inlineStr"/>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr">
+      <c r="A123" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr"/>
+      <c r="E123" s="1" t="inlineStr"/>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="H123" s="1" t="inlineStr"/>
+      <c r="I123" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr"/>
+      <c r="E124" s="1" t="inlineStr"/>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="H124" s="1" t="inlineStr"/>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t>шаг 0,5 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr"/>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>8. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n"/>
+      <c r="D125" s="1" t="n"/>
+      <c r="E125" s="1" t="n"/>
+      <c r="F125" s="1" t="n"/>
+      <c r="G125" s="1" t="n"/>
+      <c r="H125" s="1" t="n"/>
+      <c r="I125" s="1" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr"/>
+      <c r="D126" s="1" t="inlineStr"/>
+      <c r="E126" s="1" t="inlineStr"/>
+      <c r="F126" s="1" t="inlineStr"/>
+      <c r="G126" s="1" t="inlineStr"/>
+      <c r="H126" s="1" t="inlineStr"/>
+      <c r="I126" s="1" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr"/>
+      <c r="D127" s="1" t="inlineStr"/>
+      <c r="E127" s="1" t="inlineStr"/>
+      <c r="F127" s="1" t="inlineStr"/>
+      <c r="G127" s="1" t="inlineStr"/>
+      <c r="H127" s="1" t="inlineStr"/>
+      <c r="I127" s="1" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Наружные сети, домовой колодец, подключение к поселковым сетям ВК и КК — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr"/>
+      <c r="D128" s="1" t="inlineStr"/>
+      <c r="E128" s="1" t="inlineStr"/>
+      <c r="F128" s="1" t="inlineStr"/>
+      <c r="G128" s="1" t="inlineStr"/>
+      <c r="H128" s="1" t="inlineStr"/>
+      <c r="I128" s="1" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Система автополива участка (трассы, клапаны, контроллер) — по ландшафтному проекту</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr"/>
+      <c r="D129" s="1" t="inlineStr"/>
+      <c r="E129" s="1" t="inlineStr"/>
+      <c r="F129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr"/>
+      <c r="H129" s="1" t="inlineStr"/>
+      <c r="I129" s="1" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Короба, люки 600×600 и 300×400 в коробах, ниши — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr"/>
+      <c r="D130" s="1" t="inlineStr"/>
+      <c r="E130" s="1" t="inlineStr"/>
+      <c r="F130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr"/>
+      <c r="H130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1543,12 +1543,12 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>2 этаж, короб гаража, Ст.К1-1; по модели 17,1 м</t>
+          <t>внутри зданий; по модели 24,9 м</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>2 этаж, короб гаража, Ст.К1-1; по модели 10,4 м</t>
+          <t>внутри зданий; по модели 21,1 м</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>2 этаж, короб гаража, Ст.К1-1; по модели 0,6 м</t>
+          <t>внутри зданий; по модели 0,6 м</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø110×2,7</t>
+          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1636,12 +1636,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>баня, подъёмы к приборам 1 этажа; по модели 7,8 м</t>
+          <t>отводы в песчаной обсыпке; по модели 22,6 м</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø50×1,8</t>
+          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr"/>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>баня, подъёмы к приборам 1 этажа; по модели 10,1 м</t>
+          <t>сборные под плитой и выпуски; по модели 31,3 м + стояки прочисток 2 × 0,8 м</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
+          <t>Труба полипропиленовая канализационная наружная Ø110, SN8 — К2 от пескоуловителя гаража</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr"/>
@@ -1698,12 +1698,12 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 21,1 м</t>
+          <t>К2-1 (лист 4); по модели 2,1 м, отвод 2 × 45° — по месту</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
+          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1725,64 +1725,64 @@
       <c r="E44" s="1" t="inlineStr"/>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 31,3 м + стояки прочисток 2 × 0,8 м</t>
+          <t>выпуски К1-1, К1-б, К2-1 (лист 14, узел 2)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="1" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n"/>
+      <c r="D45" s="1" t="n"/>
+      <c r="E45" s="1" t="n"/>
+      <c r="F45" s="1" t="n"/>
+      <c r="G45" s="1" t="n"/>
+      <c r="H45" s="1" t="n"/>
+      <c r="I45" s="1" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32413-2013</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr">
-        <is>
-          <t>выпуски К1-1, К1-б (лист 14, узел 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="n"/>
-      <c r="D46" s="1" t="n"/>
-      <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
-      <c r="G46" s="1" t="n"/>
-      <c r="H46" s="1" t="n"/>
-      <c r="I46" s="1" t="n"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr"/>
+      <c r="E46" s="1" t="inlineStr"/>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H46" s="1" t="inlineStr"/>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>выходы коллекторов</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
+          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1868,12 +1868,12 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>выходы коллекторов</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1899,12 +1899,12 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1930,12 +1930,12 @@
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1992,12 +1992,12 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2023,12 +2023,12 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>в приямке ввода (лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2174,7 +2174,7 @@
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G59" s="1" t="n">
@@ -2183,7 +2183,7 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>в приямке ввода (лист 14, узел 1)</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2193,19 +2193,19 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr"/>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G60" s="1" t="n">
@@ -2214,7 +2214,7 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø110, 45°</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 45°</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 45°</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2307,7 +2307,7 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
@@ -2395,12 +2395,12 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2426,12 +2426,12 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели, прочистки</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2457,12 +2457,12 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2519,12 +2519,12 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>К1-1 у 1.8, К1-б у б2</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
@@ -2555,7 +2555,7 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>К1-1 у 1.8, К1-б у б2</t>
+          <t>Ст.К1-1 (+1,000), начало сборного в гараже</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
@@ -2586,7 +2586,7 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), начало сборного в гараже</t>
+          <t>прочистки в грунте</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2608,64 +2608,64 @@
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="1" t="inlineStr"/>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 40 шт.)</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n"/>
+      <c r="D74" s="1" t="n"/>
+      <c r="E74" s="1" t="n"/>
+      <c r="F74" s="1" t="n"/>
+      <c r="G74" s="1" t="n"/>
+      <c r="H74" s="1" t="n"/>
+      <c r="I74" s="1" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32414-2013</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr"/>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G74" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 40 шт.)</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="n"/>
-      <c r="D75" s="1" t="n"/>
-      <c r="E75" s="1" t="n"/>
-      <c r="F75" s="1" t="n"/>
-      <c r="G75" s="1" t="n"/>
-      <c r="H75" s="1" t="n"/>
-      <c r="I75" s="1" t="n"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr"/>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2720,12 +2720,12 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
+          <t>на Т4 у Н8, Н9</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2751,12 +2751,12 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2787,7 +2787,7 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2818,7 +2818,7 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2844,12 +2844,12 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>выход Т4 из ШВК-1 и ШВК-Б (П4)</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Кран поливочный Ду 15 с выносом через стену (сезонный)</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2875,12 +2875,12 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>выход Т4 из ШВК-1 и ШВК-Б (П4)</t>
+          <t>ПК-1…ПК-3; на зиму — перекрыть и слить</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный незамерзающий Ду 15 с выносом через стену</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2906,12 +2906,12 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2937,60 +2937,60 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="1" t="inlineStr"/>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n"/>
+      <c r="D85" s="1" t="n"/>
+      <c r="E85" s="1" t="n"/>
+      <c r="F85" s="1" t="n"/>
+      <c r="G85" s="1" t="n"/>
+      <c r="H85" s="1" t="n"/>
+      <c r="I85" s="1" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G85" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr">
-        <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="n"/>
-      <c r="D86" s="1" t="n"/>
-      <c r="E86" s="1" t="n"/>
-      <c r="F86" s="1" t="n"/>
-      <c r="G86" s="1" t="n"/>
-      <c r="H86" s="1" t="n"/>
-      <c r="I86" s="1" t="n"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>по дизайн-проекту</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr"/>
+      <c r="E86" s="1" t="inlineStr"/>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" s="1" t="inlineStr"/>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3019,7 +3019,7 @@
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>УМ-1…УМ-3, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3045,12 +3045,12 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-3, УМ-б1</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3081,7 +3081,7 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -3107,12 +3107,12 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -3134,16 +3134,16 @@
       <c r="E91" s="1" t="inlineStr"/>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr"/>
@@ -3169,12 +3169,12 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -3200,12 +3200,12 @@
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3236,7 +3236,7 @@
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -3427,27 +3427,43 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="inlineStr"/>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>7. Изоляция, гильзы и крепления</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="n"/>
-      <c r="D101" s="1" t="n"/>
-      <c r="E101" s="1" t="n"/>
-      <c r="F101" s="1" t="n"/>
-      <c r="G101" s="1" t="n"/>
-      <c r="H101" s="1" t="n"/>
-      <c r="I101" s="1" t="n"/>
+      <c r="A101" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr"/>
+      <c r="E101" s="1" t="inlineStr"/>
+      <c r="F101" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H101" s="1" t="inlineStr"/>
+      <c r="I101" s="1" t="inlineStr">
+        <is>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3459,49 +3475,33 @@
       <c r="E102" s="1" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr"/>
-      <c r="E103" s="1" t="inlineStr"/>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="H103" s="1" t="inlineStr"/>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="A103" s="1" t="inlineStr"/>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n"/>
+      <c r="D103" s="1" t="n"/>
+      <c r="E103" s="1" t="n"/>
+      <c r="F103" s="1" t="n"/>
+      <c r="G103" s="1" t="n"/>
+      <c r="H103" s="1" t="n"/>
+      <c r="I103" s="1" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -3509,28 +3509,28 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Neptun, Аквасторож или или аналог</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr"/>
       <c r="E104" s="1" t="inlineStr"/>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -3552,16 +3552,16 @@
       <c r="E105" s="1" t="inlineStr"/>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3583,16 +3583,16 @@
       <c r="E106" s="1" t="inlineStr"/>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЭ-2 — ввод В1 в баню</t>
         </is>
       </c>
     </row>
@@ -3602,28 +3602,28 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr"/>
       <c r="E107" s="1" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>ДП-1…ДП-18</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Кабель-удлинитель датчиков (системный)</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr"/>
@@ -3649,53 +3649,37 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr"/>
-      <c r="E109" s="1" t="inlineStr"/>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G109" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>в проёме фундамента</t>
-        </is>
-      </c>
+      <c r="A109" s="1" t="inlineStr"/>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>8. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n"/>
+      <c r="D109" s="1" t="n"/>
+      <c r="E109" s="1" t="n"/>
+      <c r="F109" s="1" t="n"/>
+      <c r="G109" s="1" t="n"/>
+      <c r="H109" s="1" t="n"/>
+      <c r="I109" s="1" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3711,22 +3695,22 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3742,115 +3726,115 @@
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
       <c r="E112" s="1" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 7, стены 4 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr"/>
       <c r="E113" s="1" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 25, стены 10 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr"/>
       <c r="E114" s="1" t="inlineStr"/>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 13, стены 0 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3862,26 +3846,26 @@
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3893,26 +3877,26 @@
       <c r="E116" s="1" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>ввод В1 и подводка автополива (общий проём), выпуски К1-1, К1-б (п. 8.8)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3924,26 +3908,26 @@
       <c r="E117" s="1" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>в проёме фундамента</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3955,26 +3939,26 @@
       <c r="E118" s="1" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -3986,31 +3970,31 @@
       <c r="E119" s="1" t="inlineStr"/>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr"/>
@@ -4021,27 +4005,27 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>перекрытия и плиты 7, стены 4 (лист 14)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr"/>
@@ -4052,27 +4036,27 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>перекрытия и плиты 26, стены 10 (лист 14)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr"/>
@@ -4083,22 +4067,22 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>перекрытия и плиты 13, стены 0 (лист 14)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4110,26 +4094,26 @@
       <c r="E123" s="1" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Заделка проёмов фундамента: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -4141,33 +4125,49 @@
       <c r="E124" s="1" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>450</v>
+        <v>3</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>шаг 0,5 м</t>
+          <t>ввод В1 и подводка автополива (общий проём), выпуски К1-1, К1-б (п. 8.8)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>8. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="n"/>
-      <c r="D125" s="1" t="n"/>
-      <c r="E125" s="1" t="n"/>
-      <c r="F125" s="1" t="n"/>
-      <c r="G125" s="1" t="n"/>
-      <c r="H125" s="1" t="n"/>
-      <c r="I125" s="1" t="n"/>
+      <c r="A125" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr"/>
+      <c r="E125" s="1" t="inlineStr"/>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="H125" s="1" t="inlineStr"/>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -4175,16 +4175,30 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D126" s="1" t="inlineStr"/>
       <c r="E126" s="1" t="inlineStr"/>
-      <c r="F126" s="1" t="inlineStr"/>
-      <c r="G126" s="1" t="inlineStr"/>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>133</v>
+      </c>
       <c r="H126" s="1" t="inlineStr"/>
-      <c r="I126" s="1" t="inlineStr"/>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -4192,16 +4206,30 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D127" s="1" t="inlineStr"/>
       <c r="E127" s="1" t="inlineStr"/>
-      <c r="F127" s="1" t="inlineStr"/>
-      <c r="G127" s="1" t="inlineStr"/>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="n">
+        <v>43</v>
+      </c>
       <c r="H127" s="1" t="inlineStr"/>
-      <c r="I127" s="1" t="inlineStr"/>
+      <c r="I127" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -4209,16 +4237,30 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, домовой колодец, подключение к поселковым сетям ВК и КК — раздел НВК</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D128" s="1" t="inlineStr"/>
       <c r="E128" s="1" t="inlineStr"/>
-      <c r="F128" s="1" t="inlineStr"/>
-      <c r="G128" s="1" t="inlineStr"/>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>21</v>
+      </c>
       <c r="H128" s="1" t="inlineStr"/>
-      <c r="I128" s="1" t="inlineStr"/>
+      <c r="I128" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -4226,16 +4268,30 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка (трассы, клапаны, контроллер) — по ландшафтному проекту</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D129" s="1" t="inlineStr"/>
       <c r="E129" s="1" t="inlineStr"/>
-      <c r="F129" s="1" t="inlineStr"/>
-      <c r="G129" s="1" t="inlineStr"/>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="n">
+        <v>23</v>
+      </c>
       <c r="H129" s="1" t="inlineStr"/>
-      <c r="I129" s="1" t="inlineStr"/>
+      <c r="I129" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -4243,20 +4299,213 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Короба, люки 600×600 и 300×400 в коробах, ниши — по АР (ТЗ-1)</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D130" s="1" t="inlineStr"/>
       <c r="E130" s="1" t="inlineStr"/>
-      <c r="F130" s="1" t="inlineStr"/>
-      <c r="G130" s="1" t="inlineStr"/>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr"/>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="H131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr">
+      <c r="A132" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr"/>
+      <c r="E132" s="1" t="inlineStr"/>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="H132" s="1" t="inlineStr"/>
+      <c r="I132" s="1" t="inlineStr">
+        <is>
+          <t>шаг 0,5 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>9. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n"/>
+      <c r="D133" s="1" t="n"/>
+      <c r="E133" s="1" t="n"/>
+      <c r="F133" s="1" t="n"/>
+      <c r="G133" s="1" t="n"/>
+      <c r="H133" s="1" t="n"/>
+      <c r="I133" s="1" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr"/>
+      <c r="D134" s="1" t="inlineStr"/>
+      <c r="E134" s="1" t="inlineStr"/>
+      <c r="F134" s="1" t="inlineStr"/>
+      <c r="G134" s="1" t="inlineStr"/>
+      <c r="H134" s="1" t="inlineStr"/>
+      <c r="I134" s="1" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr"/>
+      <c r="D135" s="1" t="inlineStr"/>
+      <c r="E135" s="1" t="inlineStr"/>
+      <c r="F135" s="1" t="inlineStr"/>
+      <c r="G135" s="1" t="inlineStr"/>
+      <c r="H135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Наружные сети, домовой колодец, подключение к поселковым сетям ВК и КК — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr"/>
+      <c r="D136" s="1" t="inlineStr"/>
+      <c r="E136" s="1" t="inlineStr"/>
+      <c r="F136" s="1" t="inlineStr"/>
+      <c r="G136" s="1" t="inlineStr"/>
+      <c r="H136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr"/>
+      <c r="D137" s="1" t="inlineStr"/>
+      <c r="E137" s="1" t="inlineStr"/>
+      <c r="F137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr"/>
+      <c r="H137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Обратный клапан на входе в колодец поселковой канализации, ливневая сеть участка — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr"/>
+      <c r="D138" s="1" t="inlineStr"/>
+      <c r="E138" s="1" t="inlineStr"/>
+      <c r="F138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Короба, люки 600×600 и 300×400 в коробах, ниши — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr"/>
+      <c r="D139" s="1" t="inlineStr"/>
+      <c r="E139" s="1" t="inlineStr"/>
+      <c r="F139" s="1" t="inlineStr"/>
+      <c r="G139" s="1" t="inlineStr"/>
+      <c r="H139" s="1" t="inlineStr"/>
+      <c r="I139" s="1" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -1548,7 +1548,7 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 24,9 м</t>
+          <t>внутри зданий; по модели 25,4 м</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 21,1 м</t>
+          <t>внутри зданий; по модели 21,4 м</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 22,6 м</t>
+          <t>отводы в песчаной обсыпке; по модели 23,0 м</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 31,3 м + стояки прочисток 2 × 0,8 м</t>
+          <t>сборные под плитой и выпуски; по модели 33,0 м + стояки прочисток 3 × 0,8 м</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
@@ -2519,12 +2519,12 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>К1-1 у 1.8, К1-б у б2</t>
+          <t>К1-1 в 1.7 и 1.3, К1-б в б2</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
@@ -3417,12 +3417,12 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>1.8, б2 (узел 5)</t>
+          <t>1.7, 1.3, б2 (узел 5)</t>
         </is>
       </c>
     </row>
@@ -4067,12 +4067,12 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 13, стены 0 (лист 14)</t>
+          <t>перекрытия и плиты 14, стены 0 (лист 14)</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, домовой колодец, подключение к поселковым сетям ВК и КК — раздел НВК</t>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Обратный клапан на входе в колодец поселковой канализации, ливневая сеть участка — раздел НВК</t>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr"/>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1512,12 +1512,12 @@
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 82,0, Т3 58,4 м + 10 %</t>
+          <t>по модели В1 83,9, Т3 63,8 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 21,4 м</t>
+          <t>внутри зданий; по модели 22,5 м</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 23,0 м</t>
+          <t>отводы в песчаной обсыпке; по модели 24,3 м</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2023,12 +2023,12 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>в приямке ввода (лист 14, узел 1)</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2174,7 +2174,7 @@
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G59" s="1" t="n">
@@ -2183,7 +2183,7 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>в приямке ввода (лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2193,19 +2193,19 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø110, 45°</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr"/>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G60" s="1" t="n">
@@ -2214,7 +2214,7 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 45°</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 45°</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2307,7 +2307,7 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
@@ -2395,12 +2395,12 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели, прочистки</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2426,12 +2426,12 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>повороты по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2457,12 +2457,12 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2519,12 +2519,12 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>К1-1 в 1.7 и 1.3, К1-б в б2</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
@@ -2550,12 +2550,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), начало сборного в гараже</t>
+          <t>К1-1 в 1.7 и 1.3, К1-б в б2</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
@@ -2581,12 +2581,12 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>Ст.К1-1 (+1,000), начало сборного в гараже</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2608,64 +2608,64 @@
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
+          <t>прочистки в грунте</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr"/>
+      <c r="E74" s="1" t="inlineStr"/>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
           <t>по месту</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr"/>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 40 шт.)</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="n"/>
-      <c r="D74" s="1" t="n"/>
-      <c r="E74" s="1" t="n"/>
-      <c r="F74" s="1" t="n"/>
-      <c r="G74" s="1" t="n"/>
-      <c r="H74" s="1" t="n"/>
-      <c r="I74" s="1" t="n"/>
-    </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
-        </is>
-      </c>
+      <c r="A75" s="1" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 42 шт.)</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n"/>
+      <c r="D75" s="1" t="n"/>
+      <c r="E75" s="1" t="n"/>
+      <c r="F75" s="1" t="n"/>
+      <c r="G75" s="1" t="n"/>
+      <c r="H75" s="1" t="n"/>
+      <c r="I75" s="1" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2720,12 +2720,12 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2751,12 +2751,12 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>на Т4 у Н8, Н9</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2787,7 +2787,7 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2818,7 +2818,7 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2844,12 +2844,12 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>выход Т4 из ШВК-1 и ШВК-Б (П4)</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный Ду 15 с выносом через стену (сезонный)</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2875,12 +2875,12 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3; на зиму — перекрыть и слить</t>
+          <t>выход Т4 из ШВК-1 и ШВК-Б (П4)</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Кран поливочный Ду 15 с выносом через стену (сезонный)</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2906,12 +2906,12 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>ПК-1…ПК-3; на зиму — перекрыть и слить</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2937,60 +2937,60 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
+          <t>СМ-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr"/>
+      <c r="E85" s="1" t="inlineStr"/>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H85" s="1" t="inlineStr"/>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
           <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="3" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>6. Санитарные приборы и изделия канализации</t>
         </is>
       </c>
-      <c r="C85" s="1" t="n"/>
-      <c r="D85" s="1" t="n"/>
-      <c r="E85" s="1" t="n"/>
-      <c r="F85" s="1" t="n"/>
-      <c r="G85" s="1" t="n"/>
-      <c r="H85" s="1" t="n"/>
-      <c r="I85" s="1" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>по дизайн-проекту</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
-        </is>
-      </c>
+      <c r="C86" s="1" t="n"/>
+      <c r="D86" s="1" t="n"/>
+      <c r="E86" s="1" t="n"/>
+      <c r="F86" s="1" t="n"/>
+      <c r="G86" s="1" t="n"/>
+      <c r="H86" s="1" t="n"/>
+      <c r="I86" s="1" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3019,7 +3019,7 @@
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-3, УМ-б1</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3045,12 +3045,12 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3081,7 +3081,7 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -3107,12 +3107,12 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -3134,16 +3134,16 @@
       <c r="E91" s="1" t="inlineStr"/>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr"/>
@@ -3169,12 +3169,12 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -3200,12 +3200,12 @@
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3236,7 +3236,7 @@
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3267,7 +3267,7 @@
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3293,12 +3293,12 @@
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3324,12 +3324,12 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3360,7 +3360,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr"/>
@@ -3386,12 +3386,12 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный напольный 300×300 мм под плитку, герметичный</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr"/>
@@ -3417,12 +3417,12 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>1.7, 1.3, б2 (узел 5)</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Люк ревизионный напольный 300×300 мм под плитку, герметичный</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3444,16 +3444,16 @@
       <c r="E101" s="1" t="inlineStr"/>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>1.7, 1.3, б2 (узел 5)</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3475,64 +3475,64 @@
       <c r="E102" s="1" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr"/>
+      <c r="E103" s="1" t="inlineStr"/>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="inlineStr"/>
+      <c r="I103" s="1" t="inlineStr">
+        <is>
           <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr"/>
-      <c r="B103" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr"/>
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
         </is>
       </c>
-      <c r="C103" s="1" t="n"/>
-      <c r="D103" s="1" t="n"/>
-      <c r="E103" s="1" t="n"/>
-      <c r="F103" s="1" t="n"/>
-      <c r="G103" s="1" t="n"/>
-      <c r="H103" s="1" t="n"/>
-      <c r="I103" s="1" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>Neptun, Аквасторож или или аналог</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr"/>
-      <c r="E104" s="1" t="inlineStr"/>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H104" s="1" t="inlineStr"/>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
-        </is>
-      </c>
+      <c r="C104" s="1" t="n"/>
+      <c r="D104" s="1" t="n"/>
+      <c r="E104" s="1" t="n"/>
+      <c r="F104" s="1" t="n"/>
+      <c r="G104" s="1" t="n"/>
+      <c r="H104" s="1" t="n"/>
+      <c r="I104" s="1" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Neptun, Аквасторож или или аналог</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr"/>
@@ -3556,12 +3556,12 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3592,7 +3592,7 @@
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>КЭ-2 — ввод В1 в баню</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr"/>
@@ -3618,12 +3618,12 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-18</t>
+          <t>КЭ-2 — ввод В1 в баню</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3645,64 +3645,64 @@
       <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
+          <t>ДП-1…ДП-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Кабель-удлинитель датчиков (системный)</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>той же системы</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr"/>
+      <c r="E109" s="1" t="inlineStr"/>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="H109" s="1" t="inlineStr"/>
+      <c r="I109" s="1" t="inlineStr">
+        <is>
           <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr"/>
-      <c r="B109" s="3" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr"/>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>8. Изоляция, гильзы и крепления</t>
         </is>
       </c>
-      <c r="C109" s="1" t="n"/>
-      <c r="D109" s="1" t="n"/>
-      <c r="E109" s="1" t="n"/>
-      <c r="F109" s="1" t="n"/>
-      <c r="G109" s="1" t="n"/>
-      <c r="H109" s="1" t="n"/>
-      <c r="I109" s="1" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr"/>
-      <c r="E110" s="1" t="inlineStr"/>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="H110" s="1" t="inlineStr"/>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="C110" s="1" t="n"/>
+      <c r="D110" s="1" t="n"/>
+      <c r="E110" s="1" t="n"/>
+      <c r="F110" s="1" t="n"/>
+      <c r="G110" s="1" t="n"/>
+      <c r="H110" s="1" t="n"/>
+      <c r="I110" s="1" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3912,12 +3912,12 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>в проёме фундамента</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3943,12 +3943,12 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>в проёме фундамента</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
@@ -3989,28 +3989,28 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr"/>
       <c r="E120" s="1" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 7, стены 4 (лист 14)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -4036,12 +4036,12 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 26, стены 10 (лист 14)</t>
+          <t>перекрытия и плиты 7, стены 4 (лист 14)</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4067,12 +4067,12 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 14, стены 0 (лист 14)</t>
+          <t>перекрытия и плиты 27, стены 10 (лист 14)</t>
         </is>
       </c>
     </row>
@@ -4082,28 +4082,28 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr"/>
       <c r="E123" s="1" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>перекрытия и плиты 14, стены 0 (лист 14)</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -4129,12 +4129,12 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>ввод В1 и подводка автополива (общий проём), выпуски К1-1, К1-б (п. 8.8)</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Заделка проёмов фундамента: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -4156,16 +4156,16 @@
       <c r="E125" s="1" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>ввод В1 и подводка автополива (общий проём), выпуски К1-1, К1-б (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -4377,46 +4377,60 @@
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>450</v>
+        <v>34</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr"/>
+      <c r="E133" s="1" t="inlineStr"/>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="H133" s="1" t="inlineStr"/>
+      <c r="I133" s="1" t="inlineStr">
+        <is>
           <t>шаг 0,5 м</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr"/>
-      <c r="B133" s="3" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr"/>
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>9. Не входит в ВК.СО</t>
         </is>
       </c>
-      <c r="C133" s="1" t="n"/>
-      <c r="D133" s="1" t="n"/>
-      <c r="E133" s="1" t="n"/>
-      <c r="F133" s="1" t="n"/>
-      <c r="G133" s="1" t="n"/>
-      <c r="H133" s="1" t="n"/>
-      <c r="I133" s="1" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>123</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr"/>
-      <c r="D134" s="1" t="inlineStr"/>
-      <c r="E134" s="1" t="inlineStr"/>
-      <c r="F134" s="1" t="inlineStr"/>
-      <c r="G134" s="1" t="inlineStr"/>
-      <c r="H134" s="1" t="inlineStr"/>
-      <c r="I134" s="1" t="inlineStr"/>
+      <c r="C134" s="1" t="n"/>
+      <c r="D134" s="1" t="n"/>
+      <c r="E134" s="1" t="n"/>
+      <c r="F134" s="1" t="n"/>
+      <c r="G134" s="1" t="n"/>
+      <c r="H134" s="1" t="n"/>
+      <c r="I134" s="1" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -4424,7 +4438,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr"/>
@@ -4441,7 +4455,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr"/>
@@ -4458,7 +4472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr"/>
@@ -4475,7 +4489,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr"/>
@@ -4492,7 +4506,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Короба, люки 600×600 и 300×400 в коробах, ниши — по АР (ТЗ-1)</t>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr"/>
@@ -4503,9 +4517,26 @@
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr"/>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr"/>
-      <c r="B141" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Короба, люки 600×600 и 300×400 в коробах, ниши — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr"/>
+      <c r="D140" s="1" t="inlineStr"/>
+      <c r="E140" s="1" t="inlineStr"/>
+      <c r="F140" s="1" t="inlineStr"/>
+      <c r="G140" s="1" t="inlineStr"/>
+      <c r="H140" s="1" t="inlineStr"/>
+      <c r="I140" s="1" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 33,0 м + стояки прочисток 3 × 0,8 м</t>
+          <t>сборные под плитой и выпуски; по модели 33,0 м + стояки прочисток 4 × 0,8 м</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
@@ -2550,12 +2550,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>К1-1 в 1.7 и 1.3, К1-б в б2</t>
+          <t>1.7, 1.3, б7, б2</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
@@ -2694,7 +2694,7 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
+          <t>Т3 у Б1, вход В1 в ШВК-Б</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>вход ШВК-Б, Т3/Т4 у бойлеров</t>
+          <t>Т4 у Б1 и Н8 — 2, Т3 у Б2</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3448,12 @@
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>1.7, 1.3, б2 (узел 5)</t>
+          <t>1.7, 1.3, б7, б2 (узел 5)</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Neptun, Аквасторож или или аналог</t>
+          <t>Neptun, Аквасторож, или аналог</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr"/>
@@ -4098,12 +4098,12 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 14, стены 0 (лист 14)</t>
+          <t>перекрытия и плиты 15, стены 0 (лист 14)</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,09 м³/ч, H = 0,5 м, 1~230 В, со встроенным таймером и термостатом</t>
+          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,11 м³/ч, H = 0,7 м, 1~230 В, со встроенным таймером и термостатом</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный для ГВС Н9 (баня), то же, Q = 0,14 м³/ч, H = 0,6 м</t>
+          <t>Насос циркуляционный для ГВС Н9 (баня), то же, Q = 0,15 м³/ч, H = 0,7 м</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>ШВК-2 (в коробе гаража)</t>
+          <t>ШВК-2 (с/у 2.9, ниша)</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1</t>
+          <t>ШВК-1 (с/у 1.4, ниша)</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный ¾" (Т3) на 4 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном)</t>
+          <t>Коллектор распределительный 1" (Т3) проходной на 3 выхода ¾" «евроконус» с шаровыми кранами (последний — к мойке М-1 и далее Т4)</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) на 8 выходов ¾" «евроконус» с шаровыми кранами</t>
+          <t>Коллектор распределительный 1" (В1) проходной на 6 выходов ¾" «евроконус» с шаровыми кранами</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1223,7 +1223,7 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б</t>
+          <t>ШВК-Б2 (баня, с/у б3, ниша)</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный ¾" (Т3) на 6 выходов ¾" «евроконус» с шаровыми кранами (последний — Т4)</t>
+          <t>Коллектор распределительный ¾" (Т3) проходной на 3 выхода ¾" «евроконус» с шаровыми кранами</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б</t>
+          <t>ШВК-Б2</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Группа концевая коллектора: воздухоотводчик автоматический и кран спускной</t>
+          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1276,16 +1276,16 @@
       <c r="E29" s="1" t="inlineStr"/>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>КХ, ШВК-1, ШВК-2, ШВК-Б</t>
+          <t>ШВК-Б1 (баня, б6, короб)</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный накладной ≈950×700×200 мм</t>
+          <t>Коллектор распределительный 1" (Т3) на 4 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном)</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ШРН, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1, гараж</t>
+          <t>ШВК-Б1</t>
         </is>
       </c>
     </row>
@@ -1326,231 +1326,231 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный накладной ≈1100×650×180 мм</t>
+          <t>Группа концевая коллектора: воздухоотводчик автоматический и кран спускной</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>ШРН, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr"/>
       <c r="E31" s="1" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б, б4</t>
+          <t>КХ, ШВК-1, ШВК-2, ШВК-Б1, ШВК-Б2</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr"/>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>3. Трубопроводы (по 3D-модели)</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="n"/>
-      <c r="D32" s="1" t="n"/>
-      <c r="E32" s="1" t="n"/>
-      <c r="F32" s="1" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
-      <c r="I32" s="1" t="n"/>
+      <c r="A32" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Шкаф коллекторный встраиваемый ≈900×650×120 мм с монтажной рамой</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>ШРВ, или аналог</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>ШВК-2, ниша перегородки 2.9/2.8</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Труба напорная ПЭ 100 SDR11 32×3,0 питьевая</t>
+          <t>Шкаф коллекторный встраиваемый ≈800×600×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 18599-2001</t>
+          <t>ШРВ, или аналог</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr"/>
       <c r="E33" s="1" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>ввод до приямка; по модели 1,2 м</t>
+          <t>ШВК-1, ниша стены 1.4/1.9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 32×4,4, класс 2 и ХВ, 10 бар</t>
+          <t>Шкаф коллекторный встраиваемый ≈700×600×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32415-2013, или аналог</t>
+          <t>ШРВ, или аналог</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr"/>
       <c r="E34" s="1" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 9,9 м + 10 %</t>
+          <t>ШВК-Б2, ниша перегородки б3/б4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 25×3,5, класс 2 и ХВ, 10 бар</t>
+          <t>Шкаф коллекторный ≈800×650×150 мм с монтажной рамой (в коробе АР)</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32415-2013, или аналог</t>
+          <t>ШРВ, или аналог</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr"/>
       <c r="E35" s="1" t="inlineStr"/>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 41,8, Т3 7,9 м + 10 %</t>
+          <t>ШВК-Б1, короб на перегородке б6/б7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 20×2,8, класс 2 и ХВ, 10 бар</t>
+          <t>Люк нажимной скрытый под плитку (алюминиевая рама, дверца под облицовку) по размеру ниши шкафа</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32415-2013, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr"/>
       <c r="E36" s="1" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 48,0, Т3 44,6, Т4 32,4 м + 10 %</t>
+          <t>ШВК-1, ШВК-2, ШВК-Б2 — под плитку; ШВК-Б1 — под отделку б6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 16×2,2, класс 2 и ХВ, 10 бар</t>
+          <t>Поддон под коллекторный шкаф с отбортовкой</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32415-2013, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr"/>
       <c r="E37" s="1" t="inlineStr"/>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>163</v>
+        <v>4</v>
       </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 83,9, Т3 63,8 м + 10 %</t>
+          <t>датчики ДП под шкафами (лист 14, узел 10)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Труба канализационная малошумная трёхслойная Ø110 (ПП с минеральным наполнителем)</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>внутри зданий; по модели 25,4 м</t>
-        </is>
-      </c>
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>3. Трубопроводы (по 3D-модели)</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n"/>
+      <c r="D38" s="1" t="n"/>
+      <c r="E38" s="1" t="n"/>
+      <c r="F38" s="1" t="n"/>
+      <c r="G38" s="1" t="n"/>
+      <c r="H38" s="1" t="n"/>
+      <c r="I38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Труба канализационная малошумная трёхслойная Ø50 (ПП с минеральным наполнителем)</t>
+          <t>Труба напорная ПЭ 100 SDR11 32×3,0 питьевая</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
+          <t>ГОСТ 18599-2001</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 22,5 м</t>
+          <t>ввод до приямка; по модели 1,2 м</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Труба канализационная малошумная трёхслойная Ø32 (ПП с минеральным наполнителем)</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 32×4,4, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
+          <t>ГОСТ 32415-2013, или аналог</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr"/>
@@ -1605,12 +1605,12 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 0,6 м</t>
+          <t>по модели В1 11,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 25×3,5, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32415-2013, или аналог</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr"/>
@@ -1636,12 +1636,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 24,3 м</t>
+          <t>по модели В1 59,2, Т3 31,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 20×2,8, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ 32415-2013, или аналог</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr"/>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 33,0 м + стояки прочисток 4 × 0,8 м</t>
+          <t>по модели В1 32,6, Т3 29,0, Т4 48,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная наружная Ø110, SN8 — К2 от пескоуловителя гаража</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 16×2,2, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ 32415-2013, или аналог</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr"/>
@@ -1698,12 +1698,12 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>К2-1 (лист 4); по модели 2,1 м, отвод 2 × 45° — по месту</t>
+          <t>по модели В1 65,0, Т3 38,2 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1713,182 +1713,198 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
+          <t>Труба канализационная малошумная трёхслойная Ø110 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr"/>
       <c r="E44" s="1" t="inlineStr"/>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>выпуски К1-1, К1-б, К2-1 (лист 14, узел 2)</t>
+          <t>внутри зданий; по модели 28,6 м</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="n"/>
-      <c r="D45" s="1" t="n"/>
-      <c r="E45" s="1" t="n"/>
-      <c r="F45" s="1" t="n"/>
-      <c r="G45" s="1" t="n"/>
-      <c r="H45" s="1" t="n"/>
-      <c r="I45" s="1" t="n"/>
+      <c r="A45" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Труба канализационная малошумная трёхслойная Ø50 (ПП с минеральным наполнителем)</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr"/>
+      <c r="E45" s="1" t="inlineStr"/>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="H45" s="1" t="inlineStr"/>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>внутри зданий; по модели 22,9 м</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
+          <t>Труба канализационная малошумная трёхслойная Ø32 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr"/>
       <c r="E46" s="1" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>выходы коллекторов</t>
+          <t>внутри зданий; по модели 0,6 м</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
+          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr"/>
       <c r="E47" s="1" t="inlineStr"/>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>выходы коллекторов</t>
+          <t>отводы в песчаной обсыпке; по модели 22,5 м</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
+          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr"/>
       <c r="E48" s="1" t="inlineStr"/>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>выходы коллекторов</t>
+          <t>сборные под плитой и выпуски; по модели 44,3 м + выводы прочисток в стены до +0,500 (3 шт.) 5,1 м</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Труба полипропиленовая канализационная наружная Ø110, SN8 — К2 от пескоуловителя гаража</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr"/>
       <c r="E49" s="1" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>К2-1 (лист 4); по модели 2,1 м, отвод 2 × 45° — по месту</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr"/>
@@ -1899,45 +1915,29 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
+          <t>К1-1 — выпуск (юг) и ввод линии бани (север), К1-б, К2-1 (лист 14, узел 2)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
-        </is>
-      </c>
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n"/>
+      <c r="D51" s="1" t="n"/>
+      <c r="E51" s="1" t="n"/>
+      <c r="F51" s="1" t="n"/>
+      <c r="G51" s="1" t="n"/>
+      <c r="H51" s="1" t="n"/>
+      <c r="I51" s="1" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1961,12 +1961,12 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1992,12 +1992,12 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2023,12 +2023,12 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2054,12 +2054,12 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2085,12 +2085,12 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2116,12 +2116,12 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2147,12 +2147,12 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2178,12 +2178,12 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>в приямке ввода (лист 14, узел 1)</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2205,7 +2205,7 @@
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G60" s="1" t="n">
@@ -2214,7 +2214,7 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø110, 45°</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr"/>
@@ -2240,12 +2240,12 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 45°</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr"/>
@@ -2271,12 +2271,12 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 45°</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
@@ -2302,12 +2302,12 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
@@ -2364,12 +2364,12 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>в приямке ввода (лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2379,19 +2379,19 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G66" s="1" t="n">
@@ -2400,7 +2400,7 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
@@ -2426,12 +2426,12 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели, прочистки</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
@@ -2488,12 +2488,12 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
@@ -2550,12 +2550,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>1.7, 1.3, б7, б2</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2581,12 +2581,12 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), начало сборного в гараже</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2612,12 +2612,12 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>повороты по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2639,46 +2639,62 @@
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 42 шт.)</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="n"/>
-      <c r="D75" s="1" t="n"/>
-      <c r="E75" s="1" t="n"/>
-      <c r="F75" s="1" t="n"/>
-      <c r="G75" s="1" t="n"/>
-      <c r="H75" s="1" t="n"/>
-      <c r="I75" s="1" t="n"/>
+      <c r="A75" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr"/>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>присоединения по модели</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr"/>
@@ -2689,27 +2705,27 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>Т3 у Б1, вход В1 в ШВК-Б</t>
+          <t>б6, 1.8, 1.9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr"/>
@@ -2725,22 +2741,22 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>Т4 у Б1 и Н8 — 2, Т3 у Б2</t>
+          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr"/>
@@ -2751,34 +2767,34 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>прочистки в грунте</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr"/>
       <c r="E79" s="1" t="inlineStr"/>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G79" s="1" t="n">
@@ -2787,40 +2803,24 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
-        </is>
-      </c>
+      <c r="A80" s="1" t="inlineStr"/>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 45 шт.)</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n"/>
+      <c r="D80" s="1" t="n"/>
+      <c r="E80" s="1" t="n"/>
+      <c r="F80" s="1" t="n"/>
+      <c r="G80" s="1" t="n"/>
+      <c r="H80" s="1" t="n"/>
+      <c r="I80" s="1" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2849,7 +2849,7 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>вход В1 в ШВК-2</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2875,12 +2875,12 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>выход Т4 из ШВК-1 и ШВК-Б (П4)</t>
+          <t>Т3 у Б1, вход Т3 в ШВК-2, ввод В1 в баню (ШВК-Б2)</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный Ду 15 с выносом через стену (сезонный)</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2906,12 +2906,12 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3; на зиму — перекрыть и слить</t>
+          <t>Т4 у Б1 и Н8 — 2, Т3 к смесителю мойки М-1, Т3 у Б2</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2937,12 +2937,12 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>на Т4 у Н8, Н9</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2968,111 +2968,127 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="n"/>
-      <c r="D86" s="1" t="n"/>
-      <c r="E86" s="1" t="n"/>
-      <c r="F86" s="1" t="n"/>
-      <c r="G86" s="1" t="n"/>
-      <c r="H86" s="1" t="n"/>
-      <c r="I86" s="1" t="n"/>
+      <c r="A86" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Кран спускной Ду 15 со штуцером</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr"/>
+      <c r="E86" s="1" t="inlineStr"/>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="inlineStr"/>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>КХ-8: слив подводки автополива на зиму</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr"/>
       <c r="E87" s="1" t="inlineStr"/>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr"/>
       <c r="E88" s="1" t="inlineStr"/>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-4, УМ-б1</t>
+          <t>Т4 дома — у мойки М-1, Т4 бани — в ШВК-Б1 (П4)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>Arrowhead 485 или аналог</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr"/>
       <c r="E89" s="1" t="inlineStr"/>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G89" s="1" t="n">
@@ -3081,102 +3097,86 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr"/>
       <c r="E90" s="1" t="inlineStr"/>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr"/>
       <c r="E91" s="1" t="inlineStr"/>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Смеситель настенный для наполнения СПА</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>по дизайн-проекту</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G92" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr">
-        <is>
-          <t>СПА (б7)</t>
-        </is>
-      </c>
+      <c r="A92" s="1" t="inlineStr"/>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n"/>
+      <c r="D92" s="1" t="n"/>
+      <c r="E92" s="1" t="n"/>
+      <c r="F92" s="1" t="n"/>
+      <c r="G92" s="1" t="n"/>
+      <c r="H92" s="1" t="n"/>
+      <c r="I92" s="1" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -3184,28 +3184,28 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr"/>
       <c r="E93" s="1" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3215,28 +3215,28 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr"/>
       <c r="E94" s="1" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G94" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3246,28 +3246,28 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr"/>
       <c r="E95" s="1" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3277,28 +3277,28 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr"/>
       <c r="E96" s="1" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3308,28 +3308,28 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr"/>
       <c r="E97" s="1" t="inlineStr"/>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -3386,12 +3386,12 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr"/>
@@ -3417,12 +3417,12 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный напольный 300×300 мм под плитку, герметичный</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3448,12 +3448,12 @@
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>1.7, 1.3, б7, б2 (узел 5)</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3475,16 +3475,16 @@
       <c r="E102" s="1" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -3510,42 +3510,58 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>ПУ-1, гараж (лист 4)</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="inlineStr"/>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="n"/>
-      <c r="D104" s="1" t="n"/>
-      <c r="E104" s="1" t="n"/>
-      <c r="F104" s="1" t="n"/>
-      <c r="G104" s="1" t="n"/>
-      <c r="H104" s="1" t="n"/>
-      <c r="I104" s="1" t="n"/>
+      <c r="A104" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr"/>
+      <c r="E104" s="1" t="inlineStr"/>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="inlineStr"/>
+      <c r="I104" s="1" t="inlineStr">
+        <is>
+          <t>СМ-1</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Neptun, Аквасторож, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr"/>
@@ -3556,27 +3572,27 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr"/>
@@ -3587,22 +3603,22 @@
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3618,74 +3634,74 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>КЭ-2 — ввод В1 в баню</t>
+          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr"/>
       <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>18</v>
+        <v>6.5</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-18</t>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr"/>
       <c r="E109" s="1" t="inlineStr"/>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>оценка по плану; прокладка — ЭОМ/СС</t>
+          <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3709,7 @@
       <c r="A110" s="1" t="inlineStr"/>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>8. Изоляция, гильзы и крепления</t>
+          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
         </is>
       </c>
       <c r="C110" s="1" t="n"/>
@@ -3706,42 +3722,42 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Neptun, Аквасторож, или аналог</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr"/>
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -3753,26 +3769,26 @@
       <c r="E112" s="1" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3784,62 +3800,62 @@
       <c r="E113" s="1" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЭ-2 — ввод В1 в баню</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr"/>
       <c r="E114" s="1" t="inlineStr"/>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>ДП-1…ДП-19</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Кабель-удлинитель датчиков (системный)</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr"/>
@@ -3850,45 +3866,29 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr"/>
-      <c r="E116" s="1" t="inlineStr"/>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="H116" s="1" t="inlineStr"/>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="A116" s="1" t="inlineStr"/>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>8. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n"/>
+      <c r="D116" s="1" t="n"/>
+      <c r="E116" s="1" t="n"/>
+      <c r="F116" s="1" t="n"/>
+      <c r="G116" s="1" t="n"/>
+      <c r="H116" s="1" t="n"/>
+      <c r="I116" s="1" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3943,12 +3943,12 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>в проёме фундамента</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -3974,12 +3974,12 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -4005,12 +4005,12 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4020,28 +4020,28 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr"/>
       <c r="E121" s="1" t="inlineStr"/>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 7, стены 4 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4051,28 +4051,28 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr"/>
       <c r="E122" s="1" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 27, стены 10 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4082,28 +4082,28 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr"/>
       <c r="E123" s="1" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>перекрытия и плиты 15, стены 0 (лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -4125,16 +4125,16 @@
       <c r="E124" s="1" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>в проёме фундамента</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -4156,16 +4156,16 @@
       <c r="E125" s="1" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>ввод В1 и подводка автополива (общий проём), выпуски К1-1, К1-б (п. 8.8)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -4187,16 +4187,16 @@
       <c r="E126" s="1" t="inlineStr"/>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4206,12 +4206,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr"/>
@@ -4222,12 +4222,12 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 0, стены 7 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr"/>
@@ -4253,12 +4253,12 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 22, стены 11 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr"/>
@@ -4284,12 +4284,12 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4311,16 +4311,16 @@
       <c r="E130" s="1" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Заделка проёмов фундамента и футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -4342,16 +4342,16 @@
       <c r="E131" s="1" t="inlineStr"/>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>ввод В1 и подводка автополива (общий проём), футляры К1-1 (юг, север), К1-б, К2-1 (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -4373,16 +4373,16 @@
       <c r="E132" s="1" t="inlineStr"/>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>2 проёма (ТЗ-1, лист 4)</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -4404,139 +4404,387 @@
       <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>450</v>
+        <v>2.4</v>
       </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>шаг 0,5 м</t>
+          <t>лист 6; НВК — так же во дворе</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="inlineStr"/>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>9. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="n"/>
-      <c r="D134" s="1" t="n"/>
-      <c r="E134" s="1" t="n"/>
-      <c r="F134" s="1" t="n"/>
-      <c r="G134" s="1" t="n"/>
-      <c r="H134" s="1" t="n"/>
-      <c r="I134" s="1" t="n"/>
+      <c r="A134" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr"/>
+      <c r="E134" s="1" t="inlineStr"/>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="H134" s="1" t="inlineStr"/>
+      <c r="I134" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D135" s="1" t="inlineStr"/>
       <c r="E135" s="1" t="inlineStr"/>
-      <c r="F135" s="1" t="inlineStr"/>
-      <c r="G135" s="1" t="inlineStr"/>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="n">
+        <v>110</v>
+      </c>
       <c r="H135" s="1" t="inlineStr"/>
-      <c r="I135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D136" s="1" t="inlineStr"/>
       <c r="E136" s="1" t="inlineStr"/>
-      <c r="F136" s="1" t="inlineStr"/>
-      <c r="G136" s="1" t="inlineStr"/>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="n">
+        <v>116</v>
+      </c>
       <c r="H136" s="1" t="inlineStr"/>
-      <c r="I136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D137" s="1" t="inlineStr"/>
       <c r="E137" s="1" t="inlineStr"/>
-      <c r="F137" s="1" t="inlineStr"/>
-      <c r="G137" s="1" t="inlineStr"/>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G137" s="1" t="n">
+        <v>25</v>
+      </c>
       <c r="H137" s="1" t="inlineStr"/>
-      <c r="I137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D138" s="1" t="inlineStr"/>
       <c r="E138" s="1" t="inlineStr"/>
-      <c r="F138" s="1" t="inlineStr"/>
-      <c r="G138" s="1" t="inlineStr"/>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="H138" s="1" t="inlineStr"/>
-      <c r="I138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D139" s="1" t="inlineStr"/>
       <c r="E139" s="1" t="inlineStr"/>
-      <c r="F139" s="1" t="inlineStr"/>
-      <c r="G139" s="1" t="inlineStr"/>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="H139" s="1" t="inlineStr"/>
-      <c r="I139" s="1" t="inlineStr"/>
+      <c r="I139" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Короба, люки 600×600 и 300×400 в коробах, ниши — по АР (ТЗ-1)</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D140" s="1" t="inlineStr"/>
       <c r="E140" s="1" t="inlineStr"/>
-      <c r="F140" s="1" t="inlineStr"/>
-      <c r="G140" s="1" t="inlineStr"/>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="H140" s="1" t="inlineStr"/>
-      <c r="I140" s="1" t="inlineStr"/>
+      <c r="I140" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="inlineStr"/>
+      <c r="E141" s="1" t="inlineStr"/>
+      <c r="F141" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="H141" s="1" t="inlineStr"/>
+      <c r="I141" s="1" t="inlineStr">
+        <is>
+          <t>шаг 0,5 м</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr">
+      <c r="A142" s="1" t="inlineStr"/>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>9. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n"/>
+      <c r="D142" s="1" t="n"/>
+      <c r="E142" s="1" t="n"/>
+      <c r="F142" s="1" t="n"/>
+      <c r="G142" s="1" t="n"/>
+      <c r="H142" s="1" t="n"/>
+      <c r="I142" s="1" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="inlineStr"/>
+      <c r="D143" s="1" t="inlineStr"/>
+      <c r="E143" s="1" t="inlineStr"/>
+      <c r="F143" s="1" t="inlineStr"/>
+      <c r="G143" s="1" t="inlineStr"/>
+      <c r="H143" s="1" t="inlineStr"/>
+      <c r="I143" s="1" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr"/>
+      <c r="D144" s="1" t="inlineStr"/>
+      <c r="E144" s="1" t="inlineStr"/>
+      <c r="F144" s="1" t="inlineStr"/>
+      <c r="G144" s="1" t="inlineStr"/>
+      <c r="H144" s="1" t="inlineStr"/>
+      <c r="I144" s="1" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr"/>
+      <c r="D145" s="1" t="inlineStr"/>
+      <c r="E145" s="1" t="inlineStr"/>
+      <c r="F145" s="1" t="inlineStr"/>
+      <c r="G145" s="1" t="inlineStr"/>
+      <c r="H145" s="1" t="inlineStr"/>
+      <c r="I145" s="1" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr"/>
+      <c r="D146" s="1" t="inlineStr"/>
+      <c r="E146" s="1" t="inlineStr"/>
+      <c r="F146" s="1" t="inlineStr"/>
+      <c r="G146" s="1" t="inlineStr"/>
+      <c r="H146" s="1" t="inlineStr"/>
+      <c r="I146" s="1" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr"/>
+      <c r="D147" s="1" t="inlineStr"/>
+      <c r="E147" s="1" t="inlineStr"/>
+      <c r="F147" s="1" t="inlineStr"/>
+      <c r="G147" s="1" t="inlineStr"/>
+      <c r="H147" s="1" t="inlineStr"/>
+      <c r="I147" s="1" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Ниши коллекторных шкафов, короб ШВК-Б1, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток, короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="inlineStr"/>
+      <c r="D148" s="1" t="inlineStr"/>
+      <c r="E148" s="1" t="inlineStr"/>
+      <c r="F148" s="1" t="inlineStr"/>
+      <c r="G148" s="1" t="inlineStr"/>
+      <c r="H148" s="1" t="inlineStr"/>
+      <c r="I148" s="1" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,11 м³/ч, H = 0,7 м, 1~230 В, со встроенным таймером и термостатом</t>
+          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,12 м³/ч, H = 0,7 м, 1~230 В, со встроенным таймером и термостатом</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встраиваемый ≈800×600×120 мм с монтажной рамой</t>
+          <t>Шкаф коллекторный встраиваемый ≈750×600×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1409,7 +1409,7 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1, ниша стены 1.4/1.9</t>
+          <t>ШВК-1, ниша стены 1.4/1.3</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 59,2, Т3 31,9 м + 10 %</t>
+          <t>по модели В1 61,1, Т3 33,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 32,6, Т3 29,0, Т4 48,0 м + 10 %</t>
+          <t>по модели В1 34,7, Т3 31,0, Т4 48,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 65,0, Т3 38,2 м + 10 %</t>
+          <t>по модели В1 67,0, Т3 41,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
@@ -2811,7 +2811,7 @@
       <c r="A80" s="1" t="inlineStr"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 45 шт.)</t>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 46 шт.)</t>
         </is>
       </c>
       <c r="C80" s="1" t="n"/>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
@@ -4222,12 +4222,12 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 0, стены 7 (ТЗ-1, лист 4; лист 14)</t>
+          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 22, стены 11 (ТЗ-1, лист 4; лист 14)</t>
+          <t>плиты и перекрытия 22, стены 12 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>2 проёма (ТЗ-1, лист 4)</t>
+          <t>3 проёма (ТЗ-1, лист 4)</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,12 м³/ч, H = 0,7 м, 1~230 В, со встроенным таймером и термостатом</t>
+          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,18 м³/ч, H = 0,6 м, 1~230 В, со встроенным таймером и термостатом</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Гребёнка (коллектор) Ду 32 на 8 выходов с шаровыми кранами на выходах, латунь никелированная</t>
+          <t>Гребёнка (коллектор) Ду 32 на 9 выходов с шаровыми кранами на выходах, латунь никелированная</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1068,7 +1068,7 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>КХ, топочная 1.6; КХ-8 — автополив</t>
+          <t>КХ, топочная 1.6; КХ-8 — автополив, КХ-9 — кухня</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) на 4 выхода ¾" «евроконус» с шаровыми кранами</t>
+          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) проходной на 3 выхода ¾" «евроконус» с шаровыми кранами (последний — к мойке М-1 и далее Т4)</t>
+          <t>Коллектор распределительный 1" (Т3) проходной на 3 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном)</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1605,12 +1605,12 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 11,9 м + 10 %</t>
+          <t>по модели В1 11,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 34,7, Т3 31,0, Т4 48,0 м + 10 %</t>
+          <t>по модели В1 38,3, Т3 37,9, Т4 61,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 28,6 м</t>
+          <t>внутри зданий; по модели 27,3 м</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 22,5 м</t>
+          <t>отводы в песчаной обсыпке; по модели 22,2 м</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 44,3 м + выводы прочисток в стены до +0,500 (3 шт.) 5,1 м</t>
+          <t>сборные под плитой и выпуски; по модели 44,2 м + выводы прочисток в стены до +0,500 (3 шт.) 5,1 м</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 20×2,8</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2240,12 +2240,12 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 20×2,8</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2271,12 +2271,12 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2364,12 +2364,12 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>в приямке ввода (лист 14, узел 1)</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2391,16 +2391,16 @@
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø110, 45°</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
@@ -2426,12 +2426,12 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>в приямке ввода (лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2441,28 +2441,28 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 45°</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 45°</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2519,12 +2519,12 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2550,12 +2550,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
@@ -2612,12 +2612,12 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели, прочистки</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2674,12 +2674,12 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2705,12 +2705,12 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>б6, 1.8, 1.9</t>
+          <t>повороты по модели</t>
         </is>
       </c>
     </row>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr"/>
@@ -2736,12 +2736,12 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2767,12 +2767,12 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2794,46 +2794,62 @@
       <c r="E79" s="1" t="inlineStr"/>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>б6, 1.8, 1.9</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 46 шт.)</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="n"/>
-      <c r="D80" s="1" t="n"/>
-      <c r="E80" s="1" t="n"/>
-      <c r="F80" s="1" t="n"/>
-      <c r="G80" s="1" t="n"/>
-      <c r="H80" s="1" t="n"/>
-      <c r="I80" s="1" t="n"/>
+      <c r="A80" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Ревизия канализационная малошумная Ø110</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr"/>
+      <c r="E80" s="1" t="inlineStr"/>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr"/>
@@ -2844,76 +2860,60 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>вход В1 в ШВК-2</t>
+          <t>прочистки в грунте</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr"/>
       <c r="E82" s="1" t="inlineStr"/>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>Т3 у Б1, вход Т3 в ШВК-2, ввод В1 в баню (ШВК-Б2)</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr">
-        <is>
-          <t>Т4 у Б1 и Н8 — 2, Т3 к смесителю мойки М-1, Т3 у Б2</t>
-        </is>
-      </c>
+      <c r="A83" s="1" t="inlineStr"/>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 46 шт.)</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n"/>
+      <c r="D83" s="1" t="n"/>
+      <c r="E83" s="1" t="n"/>
+      <c r="F83" s="1" t="n"/>
+      <c r="G83" s="1" t="n"/>
+      <c r="H83" s="1" t="n"/>
+      <c r="I83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2937,12 +2937,12 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>вход В1 в ШВК-2</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2968,12 +2968,12 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>Т3 у Б1, вход Т3 в ШВК-2, ввод В1 в баню (ШВК-Б2)</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -2999,12 +2999,12 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3030,12 +3030,12 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>на Т4 у Н8, Н9</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3061,12 +3061,12 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>Т4 дома — у мойки М-1, Т4 бани — в ШВК-Б1 (П4)</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>Arrowhead 485 или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr"/>
@@ -3092,12 +3092,12 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -3128,7 +3128,7 @@
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -3154,122 +3154,122 @@
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
+          <t>Т4 санузлов дома — в ШВК-1, Т4 кухни — под мойкой М-1, Т4 бани — в ШВК-Б1 (П4)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="n"/>
-      <c r="D92" s="1" t="n"/>
-      <c r="E92" s="1" t="n"/>
-      <c r="F92" s="1" t="n"/>
-      <c r="G92" s="1" t="n"/>
-      <c r="H92" s="1" t="n"/>
-      <c r="I92" s="1" t="n"/>
+      <c r="A92" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>Arrowhead 485 или аналог</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr"/>
+      <c r="E92" s="1" t="inlineStr"/>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H92" s="1" t="inlineStr"/>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr"/>
       <c r="E93" s="1" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr"/>
       <c r="E94" s="1" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G94" s="1" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-4, УМ-б1</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>по дизайн-проекту</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr"/>
-      <c r="E95" s="1" t="inlineStr"/>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G95" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H95" s="1" t="inlineStr"/>
-      <c r="I95" s="1" t="inlineStr">
-        <is>
-          <t>В-2, В-3, В-б1</t>
-        </is>
-      </c>
+      <c r="A95" s="1" t="inlineStr"/>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n"/>
+      <c r="D95" s="1" t="n"/>
+      <c r="E95" s="1" t="n"/>
+      <c r="F95" s="1" t="n"/>
+      <c r="G95" s="1" t="n"/>
+      <c r="H95" s="1" t="n"/>
+      <c r="I95" s="1" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3293,12 +3293,12 @@
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3324,12 +3324,12 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3351,16 +3351,16 @@
       <c r="E98" s="1" t="inlineStr"/>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3370,28 +3370,28 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr"/>
       <c r="E99" s="1" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3401,28 +3401,28 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr"/>
       <c r="E100" s="1" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3479,12 +3479,12 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -3510,12 +3510,12 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3546,7 +3546,7 @@
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -3577,7 +3577,7 @@
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr"/>
@@ -3603,12 +3603,12 @@
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3634,12 +3634,12 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3661,16 +3661,16 @@
       <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr"/>
@@ -3696,68 +3696,84 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>ПУ-1, гараж (лист 4)</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="inlineStr"/>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="n"/>
-      <c r="D110" s="1" t="n"/>
-      <c r="E110" s="1" t="n"/>
-      <c r="F110" s="1" t="n"/>
-      <c r="G110" s="1" t="n"/>
-      <c r="H110" s="1" t="n"/>
-      <c r="I110" s="1" t="n"/>
+      <c r="A110" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr"/>
+      <c r="E110" s="1" t="inlineStr"/>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H110" s="1" t="inlineStr"/>
+      <c r="I110" s="1" t="inlineStr">
+        <is>
+          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>Neptun, Аквасторож, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr"/>
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -3778,40 +3794,24 @@
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
+          <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr"/>
-      <c r="E113" s="1" t="inlineStr"/>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>КЭ-2 — ввод В1 в баню</t>
-        </is>
-      </c>
+      <c r="A113" s="1" t="inlineStr"/>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n"/>
+      <c r="D113" s="1" t="n"/>
+      <c r="E113" s="1" t="n"/>
+      <c r="F113" s="1" t="n"/>
+      <c r="G113" s="1" t="n"/>
+      <c r="H113" s="1" t="n"/>
+      <c r="I113" s="1" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>Neptun, Аквасторож, или аналог</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr"/>
@@ -3835,12 +3835,12 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-19</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
@@ -3850,89 +3850,105 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr"/>
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>оценка по плану; прокладка — ЭОМ/СС</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="inlineStr"/>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>8. Изоляция, гильзы и крепления</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="n"/>
-      <c r="D116" s="1" t="n"/>
-      <c r="E116" s="1" t="n"/>
-      <c r="F116" s="1" t="n"/>
-      <c r="G116" s="1" t="n"/>
-      <c r="H116" s="1" t="n"/>
-      <c r="I116" s="1" t="n"/>
+      <c r="A116" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr"/>
+      <c r="E116" s="1" t="inlineStr"/>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="1" t="inlineStr"/>
+      <c r="I116" s="1" t="inlineStr">
+        <is>
+          <t>КЭ-2 — ввод В1 в баню</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr"/>
       <c r="E117" s="1" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>ДП-1…ДП-19</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Кабель-удлинитель датчиков (системный)</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr"/>
@@ -3943,45 +3959,29 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr"/>
-      <c r="E119" s="1" t="inlineStr"/>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="A119" s="1" t="inlineStr"/>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>8. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n"/>
+      <c r="D119" s="1" t="n"/>
+      <c r="E119" s="1" t="n"/>
+      <c r="F119" s="1" t="n"/>
+      <c r="G119" s="1" t="n"/>
+      <c r="H119" s="1" t="n"/>
+      <c r="I119" s="1" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -4129,12 +4129,12 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>в проёме фундамента</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -4160,12 +4160,12 @@
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -4191,12 +4191,12 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4206,28 +4206,28 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr"/>
       <c r="E127" s="1" t="inlineStr"/>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
+          <t>в проёме фундамента</t>
         </is>
       </c>
     </row>
@@ -4237,28 +4237,28 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr"/>
       <c r="E128" s="1" t="inlineStr"/>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 22, стены 12 (ТЗ-1, лист 4; лист 14)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4268,28 +4268,28 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr"/>
       <c r="E129" s="1" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4299,28 +4299,28 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr"/>
       <c r="E130" s="1" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>плиты и перекрытия 0, стены 7 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4330,28 +4330,28 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента и футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr"/>
       <c r="E131" s="1" t="inlineStr"/>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>ввод В1 и подводка автополива (общий проём), футляры К1-1 (юг, север), К1-б, К2-1 (п. 8.8)</t>
+          <t>плиты и перекрытия 22, стены 12 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4361,28 +4361,28 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr"/>
       <c r="E132" s="1" t="inlineStr"/>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>3 проёма (ТЗ-1, лист 4)</t>
+          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -4404,16 +4404,16 @@
       <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>лист 6; НВК — так же во дворе</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Заделка проёмов фундамента и футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -4435,16 +4435,16 @@
       <c r="E134" s="1" t="inlineStr"/>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>ввод В1 и подводка автополива (общий проём), футляры К1-1 (юг, север), К1-б, К2-1 (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4466,16 +4466,16 @@
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>3 проёма (ТЗ-1, лист 4)</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4497,16 +4497,16 @@
       <c r="E136" s="1" t="inlineStr"/>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>122</v>
+        <v>2.4</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>лист 6; НВК — так же во дворе</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4656,80 +4656,122 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>450</v>
+        <v>25</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>шаг 0,5 м</t>
+          <t>шаг — лист 14</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="inlineStr"/>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>9. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="n"/>
-      <c r="D142" s="1" t="n"/>
-      <c r="E142" s="1" t="n"/>
-      <c r="F142" s="1" t="n"/>
-      <c r="G142" s="1" t="n"/>
-      <c r="H142" s="1" t="n"/>
-      <c r="I142" s="1" t="n"/>
+      <c r="A142" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr"/>
+      <c r="E142" s="1" t="inlineStr"/>
+      <c r="F142" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G142" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" s="1" t="inlineStr"/>
+      <c r="I142" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D143" s="1" t="inlineStr"/>
       <c r="E143" s="1" t="inlineStr"/>
-      <c r="F143" s="1" t="inlineStr"/>
-      <c r="G143" s="1" t="inlineStr"/>
+      <c r="F143" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="n">
+        <v>35</v>
+      </c>
       <c r="H143" s="1" t="inlineStr"/>
-      <c r="I143" s="1" t="inlineStr"/>
+      <c r="I143" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr"/>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D144" s="1" t="inlineStr"/>
       <c r="E144" s="1" t="inlineStr"/>
-      <c r="F144" s="1" t="inlineStr"/>
-      <c r="G144" s="1" t="inlineStr"/>
+      <c r="F144" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G144" s="1" t="n">
+        <v>500</v>
+      </c>
       <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr"/>
+      <c r="I144" s="1" t="inlineStr">
+        <is>
+          <t>шаг 0,5 м</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>134</v>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="inlineStr"/>
-      <c r="D145" s="1" t="inlineStr"/>
-      <c r="E145" s="1" t="inlineStr"/>
-      <c r="F145" s="1" t="inlineStr"/>
-      <c r="G145" s="1" t="inlineStr"/>
-      <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr"/>
+      <c r="A145" s="1" t="inlineStr"/>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>9. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n"/>
+      <c r="D145" s="1" t="n"/>
+      <c r="E145" s="1" t="n"/>
+      <c r="F145" s="1" t="n"/>
+      <c r="G145" s="1" t="n"/>
+      <c r="H145" s="1" t="n"/>
+      <c r="I145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -4737,7 +4779,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr"/>
@@ -4754,7 +4796,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr"/>
@@ -4771,7 +4813,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Ниши коллекторных шкафов, короб ШВК-Б1, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток, короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr"/>
@@ -4782,9 +4824,60 @@
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
     </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr"/>
+      <c r="D149" s="1" t="inlineStr"/>
+      <c r="E149" s="1" t="inlineStr"/>
+      <c r="F149" s="1" t="inlineStr"/>
+      <c r="G149" s="1" t="inlineStr"/>
+      <c r="H149" s="1" t="inlineStr"/>
+      <c r="I149" s="1" t="inlineStr"/>
+    </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
-      <c r="B150" t="inlineStr">
+      <c r="A150" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr"/>
+      <c r="D150" s="1" t="inlineStr"/>
+      <c r="E150" s="1" t="inlineStr"/>
+      <c r="F150" s="1" t="inlineStr"/>
+      <c r="G150" s="1" t="inlineStr"/>
+      <c r="H150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Ниши коллекторных шкафов, короб ШВК-Б1, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток, короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr"/>
+      <c r="D151" s="1" t="inlineStr"/>
+      <c r="E151" s="1" t="inlineStr"/>
+      <c r="F151" s="1" t="inlineStr"/>
+      <c r="G151" s="1" t="inlineStr"/>
+      <c r="H151" s="1" t="inlineStr"/>
+      <c r="I151" s="1" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,18 м³/ч, H = 0,6 м, 1~230 В, со встроенным таймером и термостатом</t>
+          <t>Насос циркуляционный для ГВС Н8 (дом), корпус — бронза или нержавеющая сталь, Q = 0,24 м³/ч, H = 0,5 м, 1~230 В, со встроенным таймером и термостатом</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный для ГВС Н9 (баня), то же, Q = 0,15 м³/ч, H = 0,7 м</t>
+          <t>Насос циркуляционный для ГВС Н9 (баня), то же, Q = 0,24 м³/ч, H = 0,7 м</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -573,7 +573,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>у Б2 (П4)</t>
+          <t>у Б2, на Т4 (П4)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Гребёнка (коллектор) Ду 32 на 9 выходов с шаровыми кранами на выходах, латунь никелированная</t>
+          <t>Гребёнка (коллектор) Ду 32 на 10 выходов с шаровыми кранами на выходах, латунь никелированная</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1068,7 +1068,7 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>КХ, топочная 1.6; КХ-8 — автополив, КХ-9 — кухня</t>
+          <t>КХ, топочная 1.6; КХ-4 — ШВК-2, КХ-10 — ШВК-1, КХ-8 — автополив, КХ-9 — кухня</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1¼" (В1) проходной на 8 выходов ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
+          <t>Коллектор распределительный 1¼" (В1) на 7 выходов ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>ШВК-2 (с/у 2.9, ниша)</t>
+          <t>ШВК-2 (с/у 2.9, ниша); вход — КХ-4</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) проходной на 6 выходов ¾" «евроконус» с шаровыми кранами</t>
+          <t>Коллектор распределительный 1" (Т3) на 6 выходов ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1130,7 +1130,7 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>ШВК-2</t>
+          <t>ШВК-2; Т4 — через Пс-2, Пс-1 к Н8</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами</t>
+          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1161,7 +1161,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1 (с/у 1.4, ниша)</t>
+          <t>ШВК-1 (с/у 1.4, ниша); вход — КХ-10</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) проходной на 3 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном)</t>
+          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1192,7 +1192,7 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1</t>
+          <t>ШВК-1; Т4 — к Н8</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) проходной на 6 выходов ¾" «евроконус» с шаровыми кранами</t>
+          <t>Коллектор распределительный 1" (В1) на 5 выходов ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1223,7 +1223,7 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б2 (баня, с/у б3, ниша)</t>
+          <t>ШВК-Б2 (баня, с/у б3, ниша); вход — Ecoflex, КЭ-2</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный ¾" (Т3) проходной на 3 выхода ¾" «евроконус» с шаровыми кранами</t>
+          <t>Коллектор распределительный ¾" (Т3) на 2 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б2</t>
+          <t>ШВК-Б2; Т4 — через Пс-б1.1, б1.2, б2 к Н9</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами</t>
+          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1285,7 +1285,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б1 (баня, б6, короб)</t>
+          <t>ШВК-Б1 (баня, б7, ниша); вход — от подъёма Ecoflex, КЭ-3</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) на 4 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном)</t>
+          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (выход к Д-б1 — начало кольца Т3–Т4 через смесители Д-б1 и М-б1), латунь никелированная</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1316,7 +1316,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б1</t>
+          <t>ШВК-Б1; кольцо — к Н9</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный ≈800×650×150 мм с монтажной рамой (в коробе АР)</t>
+          <t>Шкаф коллекторный встраиваемый ≈820×650×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1471,7 +1471,7 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б1, короб на перегородке б6/б7</t>
+          <t>ШВК-Б1, ниша в восточной стене б7 у южного угла</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1, ШВК-2, ШВК-Б2 — под плитку; ШВК-Б1 — под отделку б6</t>
+          <t>ШВК-1 (1.4), ШВК-2 (2.9), ШВК-Б2 (б3), ШВК-Б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>ввод до приямка; по модели 1,2 м</t>
+          <t>ввод: под краем плиты и сквозь плиту в футляре до перехода на PE-Xa (+0,45); по модели 2,5 м</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 11,7 м + 10 %</t>
+          <t>по модели В1 10,2 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 61,1, Т3 33,7 м + 10 %</t>
+          <t>по модели В1 69,6, Т3 41,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 38,3, Т3 37,9, Т4 61,0 м + 10 %</t>
+          <t>по модели В1 36,6, Т3 63,7, Т4 67,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 67,0, Т3 41,7 м + 10 %</t>
+          <t>по модели В1 69,6, Т3 24,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 27,3 м</t>
+          <t>внутри зданий; по модели 26,9 м</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 22,9 м</t>
+          <t>внутри зданий; по модели 24,2 м</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 22,2 м</t>
+          <t>отводы в песчаной обсыпке; по модели 25,9 м</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 44,2 м + выводы прочисток в стены до +0,500 (3 шт.) 5,1 м</t>
+          <t>сборные под плитой и выпуски; по модели 42,3 м + выводы прочисток до +0,200 (3 шт.) 4,2 м</t>
         </is>
       </c>
     </row>
@@ -1915,42 +1915,58 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>К1-1 — выпуск (юг) и ввод линии бани (север), К1-б, К2-1 (лист 14, узел 2)</t>
+          <t>К1-1 — выпуск (юг) и ввод линии бани (север); баня — выпуски К1-б и К1-бв; К2-1 (лист 14, узел 2)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="n"/>
-      <c r="D51" s="1" t="n"/>
-      <c r="E51" s="1" t="n"/>
-      <c r="F51" s="1" t="n"/>
-      <c r="G51" s="1" t="n"/>
-      <c r="H51" s="1" t="n"/>
-      <c r="I51" s="1" t="n"/>
+      <c r="A51" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Футляр из трубы ПЭ 100 SDR17 75×4,5 (техническая) — ввод без приямка: под краем плиты и сквозь плиту, закладывается до бетонирования</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 18599-2001</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>ввод В1 2,1 м, КХ-8 2,5 м по оси, от 0,15 м за наружной гранью до +0,03 (лист 14, узел 1; ТЗ-1)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
+          <t>Отвод ПЭ Ø75, 90°, радиус по оси не менее 0,3 м (≥ 8 d трубы в футляре) — гнутый или сварной</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 18599-2001</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr"/>
@@ -1961,45 +1977,29 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>выходы коллекторов</t>
+          <t>ввод В1 — 1, КХ-8 — 2; трубу можно вынуть без вскрытия плиты</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>выходы коллекторов</t>
-        </is>
-      </c>
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>4. Фасонные части (подсчёт по 3D-модели)</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n"/>
+      <c r="D53" s="1" t="n"/>
+      <c r="E53" s="1" t="n"/>
+      <c r="F53" s="1" t="n"/>
+      <c r="G53" s="1" t="n"/>
+      <c r="H53" s="1" t="n"/>
+      <c r="I53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2054,12 +2054,12 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2085,12 +2085,12 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2147,12 +2147,12 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
+          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2178,12 +2178,12 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 20×2,8</t>
+          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2209,12 +2209,12 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 20×2,8</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 25×3,5</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2302,12 +2302,12 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2333,12 +2333,12 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 20×2,8</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2364,12 +2364,12 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 25×3,5</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2400,7 +2400,7 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2426,12 +2426,12 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>в приямке ввода (лист 14, узел 1)</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2453,16 +2453,16 @@
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø110, 45°</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
@@ -2488,12 +2488,12 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 45°</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
@@ -2519,12 +2519,12 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 45°</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
@@ -2550,12 +2550,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>в 1.6 над полом (+0,45), под краном на вводе (лист 7; лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2565,28 +2565,28 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2612,12 +2612,12 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты и низ подъёмов по модели</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2643,12 +2643,12 @@
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты и низ подъёмов по модели</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Отвод канализационный малошумный Ø50, 30°</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr"/>
@@ -2674,12 +2674,12 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели, прочистки</t>
+          <t>повороты и низ подъёмов по модели</t>
         </is>
       </c>
     </row>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr"/>
@@ -2710,7 +2710,7 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>повороты по модели</t>
+          <t>повороты и низ подъёмов по модели</t>
         </is>
       </c>
     </row>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Отвод канализационный малошумный Ø32, 30°</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr"/>
@@ -2736,12 +2736,12 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты и низ подъёмов по модели</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr"/>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr"/>
@@ -2798,12 +2798,12 @@
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>б6, 1.8, 1.9</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2829,12 +2829,12 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2860,12 +2860,12 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>повороты, низ подъёмов и стояков по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Отвод ПП канализационный Ø110, 15°</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2887,7 +2887,7 @@
       <c r="E82" s="1" t="inlineStr"/>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G82" s="1" t="n">
@@ -2896,37 +2896,53 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>К1-б: поворот 60° в б6 — 45° + 15°</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 46 шт.)</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="n"/>
-      <c r="D83" s="1" t="n"/>
-      <c r="E83" s="1" t="n"/>
-      <c r="F83" s="1" t="n"/>
-      <c r="G83" s="1" t="n"/>
-      <c r="H83" s="1" t="n"/>
-      <c r="I83" s="1" t="n"/>
+      <c r="A83" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr"/>
+      <c r="E83" s="1" t="inlineStr"/>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H83" s="1" t="inlineStr"/>
+      <c r="I83" s="1" t="inlineStr">
+        <is>
+          <t>повороты, низ подъёмов и стояков по модели</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
+          <t>Отвод ПП канализационный Ø50, 30°</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr"/>
@@ -2942,22 +2958,22 @@
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>вход В1 в ШВК-2</t>
+          <t>К1-М-б1 у стояка</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Отвод ПП канализационный Ø50, 15°</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr"/>
@@ -2968,27 +2984,27 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>Т3 у Б1, вход Т3 в ШВК-2, ввод В1 в баню (ШВК-Б2)</t>
+          <t>К1-ГБ-Б2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr"/>
@@ -2999,27 +3015,27 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr"/>
@@ -3030,27 +3046,27 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr"/>
@@ -3061,27 +3077,27 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr"/>
@@ -3092,27 +3108,27 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>б6, 1.8, 1.9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr"/>
@@ -3128,22 +3144,22 @@
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr"/>
@@ -3159,22 +3175,22 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>Т4 санузлов дома — в ШВК-1, Т4 кухни — под мойкой М-1, Т4 бани — в ШВК-Б1 (П4)</t>
+          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Arrowhead 485 или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr"/>
@@ -3190,29 +3206,29 @@
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
+          <t>прочистки в грунте</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr"/>
       <c r="E93" s="1" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G93" s="1" t="n">
@@ -3221,223 +3237,223 @@
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr"/>
-      <c r="E94" s="1" t="inlineStr"/>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr">
-        <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
-        </is>
-      </c>
+      <c r="A94" s="1" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n"/>
+      <c r="D94" s="1" t="n"/>
+      <c r="E94" s="1" t="n"/>
+      <c r="F94" s="1" t="n"/>
+      <c r="G94" s="1" t="n"/>
+      <c r="H94" s="1" t="n"/>
+      <c r="I94" s="1" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr"/>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="n"/>
-      <c r="D95" s="1" t="n"/>
-      <c r="E95" s="1" t="n"/>
-      <c r="F95" s="1" t="n"/>
-      <c r="G95" s="1" t="n"/>
-      <c r="H95" s="1" t="n"/>
-      <c r="I95" s="1" t="n"/>
+      <c r="A95" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr"/>
+      <c r="E95" s="1" t="inlineStr"/>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="1" t="inlineStr"/>
+      <c r="I95" s="1" t="inlineStr">
+        <is>
+          <t>вход В1 в ШВК-2</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr"/>
       <c r="E96" s="1" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr"/>
       <c r="E97" s="1" t="inlineStr"/>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-4, УМ-б1</t>
+          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr"/>
       <c r="E98" s="1" t="inlineStr"/>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>на Т4 у Н8, Н9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr"/>
       <c r="E99" s="1" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr"/>
       <c r="E100" s="1" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr"/>
@@ -3453,17 +3469,17 @@
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3479,27 +3495,27 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Arrowhead 485 или аналог</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr"/>
@@ -3510,22 +3526,22 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3546,17 +3562,17 @@
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -3572,45 +3588,29 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr"/>
-      <c r="E106" s="1" t="inlineStr"/>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
-        </is>
-      </c>
+      <c r="A106" s="1" t="inlineStr"/>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n"/>
+      <c r="D106" s="1" t="n"/>
+      <c r="E106" s="1" t="n"/>
+      <c r="F106" s="1" t="n"/>
+      <c r="G106" s="1" t="n"/>
+      <c r="H106" s="1" t="n"/>
+      <c r="I106" s="1" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -3618,28 +3618,28 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr"/>
       <c r="E107" s="1" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3649,28 +3649,28 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr"/>
       <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3680,28 +3680,28 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr"/>
       <c r="E109" s="1" t="inlineStr"/>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3711,28 +3711,28 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr"/>
       <c r="E110" s="1" t="inlineStr"/>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3742,28 +3742,28 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr"/>
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
@@ -3794,37 +3794,53 @@
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>ПУ-1, гараж (лист 4)</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr"/>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="n"/>
-      <c r="D113" s="1" t="n"/>
-      <c r="E113" s="1" t="n"/>
-      <c r="F113" s="1" t="n"/>
-      <c r="G113" s="1" t="n"/>
-      <c r="H113" s="1" t="n"/>
-      <c r="I113" s="1" t="n"/>
+      <c r="A113" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr"/>
+      <c r="E113" s="1" t="inlineStr"/>
+      <c r="F113" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr">
+        <is>
+          <t>Д-3, Д-б1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>Neptun, Аквасторож, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr"/>
@@ -3835,22 +3851,22 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3871,17 +3887,17 @@
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3902,22 +3918,22 @@
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>КЭ-2 — ввод В1 в баню</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr"/>
@@ -3928,68 +3944,84 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-19</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr"/>
       <c r="E118" s="1" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>оценка по плану; прокладка — ЭОМ/СС</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr"/>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>8. Изоляция, гильзы и крепления</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="n"/>
-      <c r="D119" s="1" t="n"/>
-      <c r="E119" s="1" t="n"/>
-      <c r="F119" s="1" t="n"/>
-      <c r="G119" s="1" t="n"/>
-      <c r="H119" s="1" t="n"/>
-      <c r="I119" s="1" t="n"/>
+      <c r="A119" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr"/>
+      <c r="E119" s="1" t="inlineStr"/>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" s="1" t="inlineStr"/>
+      <c r="I119" s="1" t="inlineStr">
+        <is>
+          <t>сброс ГБ Б2</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -4001,57 +4033,57 @@
       <c r="E120" s="1" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr"/>
       <c r="E121" s="1" t="inlineStr"/>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4063,26 +4095,26 @@
       <c r="E122" s="1" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4098,22 +4130,22 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>74</v>
+        <v>6.5</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -4125,88 +4157,72 @@
       <c r="E124" s="1" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr"/>
-      <c r="E125" s="1" t="inlineStr"/>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="A125" s="1" t="inlineStr"/>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n"/>
+      <c r="D125" s="1" t="n"/>
+      <c r="E125" s="1" t="n"/>
+      <c r="F125" s="1" t="n"/>
+      <c r="G125" s="1" t="n"/>
+      <c r="H125" s="1" t="n"/>
+      <c r="I125" s="1" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Neptun, Аквасторож, или аналог</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr"/>
       <c r="E126" s="1" t="inlineStr"/>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная Ø35×13 мм — ввод ПЭ 32</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -4218,26 +4234,26 @@
       <c r="E127" s="1" t="inlineStr"/>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>в проёме фундамента</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -4249,111 +4265,95 @@
       <c r="E128" s="1" t="inlineStr"/>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr"/>
       <c r="E129" s="1" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>ДП-1…ДП-19</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Кабель-удлинитель датчиков (системный)</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr"/>
       <c r="E130" s="1" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>7</v>
+        <v>180</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 0, стены 7 (ТЗ-1, лист 4; лист 14)</t>
+          <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32414-2013</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr"/>
-      <c r="E131" s="1" t="inlineStr"/>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>плиты и перекрытия 22, стены 12 (ТЗ-1, лист 4; лист 14)</t>
-        </is>
-      </c>
+      <c r="A131" s="1" t="inlineStr"/>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>8. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n"/>
+      <c r="D131" s="1" t="n"/>
+      <c r="E131" s="1" t="n"/>
+      <c r="F131" s="1" t="n"/>
+      <c r="G131" s="1" t="n"/>
+      <c r="H131" s="1" t="n"/>
+      <c r="I131" s="1" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -4361,28 +4361,28 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr"/>
       <c r="E132" s="1" t="inlineStr"/>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -4404,16 +4404,16 @@
       <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов фундамента и футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -4435,16 +4435,16 @@
       <c r="E134" s="1" t="inlineStr"/>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>ввод В1 и подводка автополива (общий проём), футляры К1-1 (юг, север), К1-б, К2-1 (п. 8.8)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4466,16 +4466,16 @@
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>3 проёма (ТЗ-1, лист 4)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4497,16 +4497,16 @@
       <c r="E136" s="1" t="inlineStr"/>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>2.4</v>
+        <v>41</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>лист 6; НВК — так же во дворе</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4528,16 +4528,16 @@
       <c r="E137" s="1" t="inlineStr"/>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4559,16 +4559,16 @@
       <c r="E138" s="1" t="inlineStr"/>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>105</v>
+        <v>12</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4590,16 +4590,16 @@
       <c r="E139" s="1" t="inlineStr"/>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -4621,16 +4621,16 @@
       <c r="E140" s="1" t="inlineStr"/>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr"/>
@@ -4656,12 +4656,12 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 0, стены 7 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4671,12 +4671,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr"/>
@@ -4687,12 +4687,12 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 20, стены 9 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4702,12 +4702,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr"/>
@@ -4718,12 +4718,12 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -4745,139 +4745,511 @@
       <c r="E144" s="1" t="inlineStr"/>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>шаг 0,5 м</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="inlineStr"/>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>9. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="n"/>
-      <c r="D145" s="1" t="n"/>
-      <c r="E145" s="1" t="n"/>
-      <c r="F145" s="1" t="n"/>
-      <c r="G145" s="1" t="n"/>
-      <c r="H145" s="1" t="n"/>
-      <c r="I145" s="1" t="n"/>
+      <c r="A145" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr"/>
+      <c r="E145" s="1" t="inlineStr"/>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G145" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H145" s="1" t="inlineStr"/>
+      <c r="I145" s="1" t="inlineStr">
+        <is>
+          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C146" s="1" t="inlineStr"/>
+          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D146" s="1" t="inlineStr"/>
       <c r="E146" s="1" t="inlineStr"/>
-      <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr"/>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G146" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr"/>
+      <c r="I146" s="1" t="inlineStr">
+        <is>
+          <t>3 проёма (ТЗ-1, лист 4)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
-        </is>
-      </c>
-      <c r="C147" s="1" t="inlineStr"/>
+          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D147" s="1" t="inlineStr"/>
       <c r="E147" s="1" t="inlineStr"/>
-      <c r="F147" s="1" t="inlineStr"/>
-      <c r="G147" s="1" t="inlineStr"/>
+      <c r="F147" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G147" s="1" t="n">
+        <v>2.4</v>
+      </c>
       <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr"/>
+      <c r="I147" s="1" t="inlineStr">
+        <is>
+          <t>лист 6; НВК — так же во дворе</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
-        </is>
-      </c>
-      <c r="C148" s="1" t="inlineStr"/>
+          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D148" s="1" t="inlineStr"/>
       <c r="E148" s="1" t="inlineStr"/>
-      <c r="F148" s="1" t="inlineStr"/>
-      <c r="G148" s="1" t="inlineStr"/>
+      <c r="F148" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G148" s="1" t="n">
+        <v>3.1</v>
+      </c>
       <c r="H148" s="1" t="inlineStr"/>
-      <c r="I148" s="1" t="inlineStr"/>
+      <c r="I148" s="1" t="inlineStr">
+        <is>
+          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
-        </is>
-      </c>
-      <c r="C149" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D149" s="1" t="inlineStr"/>
       <c r="E149" s="1" t="inlineStr"/>
-      <c r="F149" s="1" t="inlineStr"/>
-      <c r="G149" s="1" t="inlineStr"/>
+      <c r="F149" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G149" s="1" t="n">
+        <v>36</v>
+      </c>
       <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr"/>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
-        </is>
-      </c>
-      <c r="C150" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D150" s="1" t="inlineStr"/>
       <c r="E150" s="1" t="inlineStr"/>
-      <c r="F150" s="1" t="inlineStr"/>
-      <c r="G150" s="1" t="inlineStr"/>
+      <c r="F150" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G150" s="1" t="n">
+        <v>81</v>
+      </c>
       <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Ниши коллекторных шкафов, короб ШВК-Б1, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток, короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
-        </is>
-      </c>
-      <c r="C151" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D151" s="1" t="inlineStr"/>
       <c r="E151" s="1" t="inlineStr"/>
-      <c r="F151" s="1" t="inlineStr"/>
-      <c r="G151" s="1" t="inlineStr"/>
+      <c r="F151" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G151" s="1" t="n">
+        <v>89</v>
+      </c>
       <c r="H151" s="1" t="inlineStr"/>
-      <c r="I151" s="1" t="inlineStr"/>
+      <c r="I151" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr"/>
+      <c r="E152" s="1" t="inlineStr"/>
+      <c r="F152" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G152" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H152" s="1" t="inlineStr"/>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
-      <c r="B153" t="inlineStr">
+      <c r="A153" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr"/>
+      <c r="E153" s="1" t="inlineStr"/>
+      <c r="F153" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G153" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H153" s="1" t="inlineStr"/>
+      <c r="I153" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="inlineStr"/>
+      <c r="E154" s="1" t="inlineStr"/>
+      <c r="F154" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G154" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" s="1" t="inlineStr"/>
+      <c r="I154" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr"/>
+      <c r="E155" s="1" t="inlineStr"/>
+      <c r="F155" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G155" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="H155" s="1" t="inlineStr"/>
+      <c r="I155" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr"/>
+      <c r="E156" s="1" t="inlineStr"/>
+      <c r="F156" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>650</v>
+      </c>
+      <c r="H156" s="1" t="inlineStr"/>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
+          <t>шаг 0,5 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr"/>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>9. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="n"/>
+      <c r="D157" s="1" t="n"/>
+      <c r="E157" s="1" t="n"/>
+      <c r="F157" s="1" t="n"/>
+      <c r="G157" s="1" t="n"/>
+      <c r="H157" s="1" t="n"/>
+      <c r="I157" s="1" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr"/>
+      <c r="D158" s="1" t="inlineStr"/>
+      <c r="E158" s="1" t="inlineStr"/>
+      <c r="F158" s="1" t="inlineStr"/>
+      <c r="G158" s="1" t="inlineStr"/>
+      <c r="H158" s="1" t="inlineStr"/>
+      <c r="I158" s="1" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr"/>
+      <c r="D159" s="1" t="inlineStr"/>
+      <c r="E159" s="1" t="inlineStr"/>
+      <c r="F159" s="1" t="inlineStr"/>
+      <c r="G159" s="1" t="inlineStr"/>
+      <c r="H159" s="1" t="inlineStr"/>
+      <c r="I159" s="1" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr"/>
+      <c r="D160" s="1" t="inlineStr"/>
+      <c r="E160" s="1" t="inlineStr"/>
+      <c r="F160" s="1" t="inlineStr"/>
+      <c r="G160" s="1" t="inlineStr"/>
+      <c r="H160" s="1" t="inlineStr"/>
+      <c r="I160" s="1" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr"/>
+      <c r="D161" s="1" t="inlineStr"/>
+      <c r="E161" s="1" t="inlineStr"/>
+      <c r="F161" s="1" t="inlineStr"/>
+      <c r="G161" s="1" t="inlineStr"/>
+      <c r="H161" s="1" t="inlineStr"/>
+      <c r="I161" s="1" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr"/>
+      <c r="D162" s="1" t="inlineStr"/>
+      <c r="E162" s="1" t="inlineStr"/>
+      <c r="F162" s="1" t="inlineStr"/>
+      <c r="G162" s="1" t="inlineStr"/>
+      <c r="H162" s="1" t="inlineStr"/>
+      <c r="I162" s="1" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr"/>
+      <c r="D163" s="1" t="inlineStr"/>
+      <c r="E163" s="1" t="inlineStr"/>
+      <c r="F163" s="1" t="inlineStr"/>
+      <c r="G163" s="1" t="inlineStr"/>
+      <c r="H163" s="1" t="inlineStr"/>
+      <c r="I163" s="1" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1641,7 +1641,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 69,6, Т3 41,9 м + 10 %</t>
+          <t>по модели В1 69,5, Т3 41,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 36,6, Т3 63,7, Т4 67,0 м + 10 %</t>
+          <t>по модели В1 37,9, Т3 63,7, Т4 67,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 25,9 м</t>
+          <t>отводы в песчаной обсыпке; по модели 26,1 м</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 15°</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2984,12 +2984,12 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>К1-ГБ-Б2</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3082,7 +3082,7 @@
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>б6, 1.8, 1.9</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3108,12 +3108,12 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>б6, 1.8, 1.9</t>
+          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr"/>
@@ -3139,12 +3139,12 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
+          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr"/>
@@ -3175,7 +3175,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
+          <t>прочистки в грунте</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3197,64 +3197,64 @@
       <c r="E92" s="1" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="1" t="inlineStr"/>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n"/>
+      <c r="D93" s="1" t="n"/>
+      <c r="E93" s="1" t="n"/>
+      <c r="F93" s="1" t="n"/>
+      <c r="G93" s="1" t="n"/>
+      <c r="H93" s="1" t="n"/>
+      <c r="I93" s="1" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 32414-2013</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G93" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr"/>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="n"/>
-      <c r="D94" s="1" t="n"/>
-      <c r="E94" s="1" t="n"/>
-      <c r="F94" s="1" t="n"/>
-      <c r="G94" s="1" t="n"/>
-      <c r="H94" s="1" t="n"/>
-      <c r="I94" s="1" t="n"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr"/>
+      <c r="E94" s="1" t="inlineStr"/>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="1" t="inlineStr"/>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>вход В1 в ШВК-2</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3278,12 +3278,12 @@
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>вход В1 в ШВК-2</t>
+          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3309,12 +3309,12 @@
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
+          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3340,12 +3340,12 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
+          <t>на Т4 у Н8, Н9</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3371,12 +3371,12 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -3407,7 +3407,7 @@
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -3438,7 +3438,7 @@
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3464,12 +3464,12 @@
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Arrowhead 485 или аналог</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr"/>
@@ -3495,12 +3495,12 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
+          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
         </is>
       </c>
     </row>
@@ -3510,12 +3510,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Arrowhead 485 или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr"/>
@@ -3526,12 +3526,12 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3557,60 +3557,60 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="1" t="inlineStr"/>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n"/>
+      <c r="D105" s="1" t="n"/>
+      <c r="E105" s="1" t="n"/>
+      <c r="F105" s="1" t="n"/>
+      <c r="G105" s="1" t="n"/>
+      <c r="H105" s="1" t="n"/>
+      <c r="I105" s="1" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr"/>
-      <c r="E105" s="1" t="inlineStr"/>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H105" s="1" t="inlineStr"/>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr"/>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="n"/>
-      <c r="D106" s="1" t="n"/>
-      <c r="E106" s="1" t="n"/>
-      <c r="F106" s="1" t="n"/>
-      <c r="G106" s="1" t="n"/>
-      <c r="H106" s="1" t="n"/>
-      <c r="I106" s="1" t="n"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>по дизайн-проекту</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr"/>
+      <c r="E106" s="1" t="inlineStr"/>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" s="1" t="inlineStr"/>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3634,12 +3634,12 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3665,12 +3665,12 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-4, УМ-б1</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3701,7 +3701,7 @@
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3727,12 +3727,12 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3754,16 +3754,16 @@
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
@@ -3789,12 +3789,12 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3820,12 +3820,12 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3856,7 +3856,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3887,7 +3887,7 @@
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3913,12 +3913,12 @@
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3944,12 +3944,12 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3980,7 +3980,7 @@
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -4011,7 +4011,7 @@
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr"/>
@@ -4037,12 +4037,12 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr"/>
@@ -4068,12 +4068,12 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4095,16 +4095,16 @@
       <c r="E122" s="1" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4126,64 +4126,64 @@
       <c r="E123" s="1" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="1" t="inlineStr"/>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n"/>
+      <c r="D124" s="1" t="n"/>
+      <c r="E124" s="1" t="n"/>
+      <c r="F124" s="1" t="n"/>
+      <c r="G124" s="1" t="n"/>
+      <c r="H124" s="1" t="n"/>
+      <c r="I124" s="1" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr"/>
-      <c r="E124" s="1" t="inlineStr"/>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="1" t="inlineStr"/>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>ПУ-1, гараж (лист 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="inlineStr"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="n"/>
-      <c r="D125" s="1" t="n"/>
-      <c r="E125" s="1" t="n"/>
-      <c r="F125" s="1" t="n"/>
-      <c r="G125" s="1" t="n"/>
-      <c r="H125" s="1" t="n"/>
-      <c r="I125" s="1" t="n"/>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>Neptun, Аквасторож, или аналог</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr"/>
+      <c r="E125" s="1" t="inlineStr"/>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" s="1" t="inlineStr"/>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Neptun, Аквасторож, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr"/>
@@ -4207,12 +4207,12 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -4238,12 +4238,12 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
+          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr"/>
@@ -4269,12 +4269,12 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
+          <t>ДП-1…ДП-19</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Кабель-удлинитель датчиков (системный)</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -4296,64 +4296,64 @@
       <c r="E129" s="1" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-19</t>
+          <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="1" t="inlineStr"/>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>8. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n"/>
+      <c r="D130" s="1" t="n"/>
+      <c r="E130" s="1" t="n"/>
+      <c r="F130" s="1" t="n"/>
+      <c r="G130" s="1" t="n"/>
+      <c r="H130" s="1" t="n"/>
+      <c r="I130" s="1" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>той же системы</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr"/>
-      <c r="E130" s="1" t="inlineStr"/>
-      <c r="F130" s="1" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr"/>
+      <c r="F131" s="1" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G130" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>оценка по плану; прокладка — ЭОМ/СС</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr"/>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>8. Изоляция, гильзы и крепления</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="n"/>
-      <c r="D131" s="1" t="n"/>
-      <c r="E131" s="1" t="n"/>
-      <c r="F131" s="1" t="n"/>
-      <c r="G131" s="1" t="n"/>
-      <c r="H131" s="1" t="n"/>
-      <c r="I131" s="1" t="n"/>
+      <c r="G131" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="H131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4563,12 +4563,12 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
@@ -4609,28 +4609,28 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr"/>
       <c r="E140" s="1" t="inlineStr"/>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4656,12 +4656,12 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 0, стены 7 (ТЗ-1, лист 4; лист 14)</t>
+          <t>плиты и перекрытия 20, стены 9 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -4687,12 +4687,12 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 20, стены 9 (ТЗ-1, лист 4; лист 14)</t>
+          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4702,28 +4702,28 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr"/>
       <c r="E143" s="1" t="inlineStr"/>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -4749,12 +4749,12 @@
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -4780,12 +4780,12 @@
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
+          <t>3 проёма (ТЗ-1, лист 4)</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
+          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -4807,16 +4807,16 @@
       <c r="E146" s="1" t="inlineStr"/>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>3 проёма (ТЗ-1, лист 4)</t>
+          <t>лист 6; НВК — так же во дворе</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
+          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -4842,12 +4842,12 @@
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>лист 6; НВК — так же во дворе</t>
+          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -4869,16 +4869,16 @@
       <c r="E148" s="1" t="inlineStr"/>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>3.1</v>
+        <v>36</v>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
+          <t>шаг — лист 14</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="G149" s="1" t="n">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="G151" s="1" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="G154" s="1" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -5090,60 +5090,46 @@
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>39</v>
+        <v>650</v>
       </c>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>шаг 0,5 м</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="1" t="inlineStr"/>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>9. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="n"/>
+      <c r="D156" s="1" t="n"/>
+      <c r="E156" s="1" t="n"/>
+      <c r="F156" s="1" t="n"/>
+      <c r="G156" s="1" t="n"/>
+      <c r="H156" s="1" t="n"/>
+      <c r="I156" s="1" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
-        </is>
-      </c>
-      <c r="C156" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D156" s="1" t="inlineStr"/>
-      <c r="E156" s="1" t="inlineStr"/>
-      <c r="F156" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G156" s="1" t="n">
-        <v>650</v>
-      </c>
-      <c r="H156" s="1" t="inlineStr"/>
-      <c r="I156" s="1" t="inlineStr">
-        <is>
-          <t>шаг 0,5 м</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="inlineStr"/>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>9. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C157" s="1" t="n"/>
-      <c r="D157" s="1" t="n"/>
-      <c r="E157" s="1" t="n"/>
-      <c r="F157" s="1" t="n"/>
-      <c r="G157" s="1" t="n"/>
-      <c r="H157" s="1" t="n"/>
-      <c r="I157" s="1" t="n"/>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr"/>
+      <c r="D157" s="1" t="inlineStr"/>
+      <c r="E157" s="1" t="inlineStr"/>
+      <c r="F157" s="1" t="inlineStr"/>
+      <c r="G157" s="1" t="inlineStr"/>
+      <c r="H157" s="1" t="inlineStr"/>
+      <c r="I157" s="1" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -5151,7 +5137,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr"/>
@@ -5168,7 +5154,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr"/>
@@ -5185,7 +5171,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr"/>
@@ -5202,7 +5188,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr"/>
@@ -5219,7 +5205,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr"/>
@@ -5230,26 +5216,9 @@
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
-        </is>
-      </c>
-      <c r="C163" s="1" t="inlineStr"/>
-      <c r="D163" s="1" t="inlineStr"/>
-      <c r="E163" s="1" t="inlineStr"/>
-      <c r="F163" s="1" t="inlineStr"/>
-      <c r="G163" s="1" t="inlineStr"/>
-      <c r="H163" s="1" t="inlineStr"/>
-      <c r="I163" s="1" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Группа безопасности бойлера 6 бар с обратным клапаном и воронкой</t>
+          <t>Группа безопасности бойлера 6 бар с обратным клапаном</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -635,7 +635,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Б2</t>
+          <t>Б2, в выгородке; воронка сброса — в разделе 6</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,11 @@
         <v>1</v>
       </c>
       <c r="H19" s="1" t="inlineStr"/>
-      <c r="I19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>за краном после счётчика</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -993,7 +997,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Фильтр тонкой очистки самопромывной Ду 32, 100 мкм, с манометром</t>
+          <t>Кран шаровой контрольный Ду 15 со штуцером (спускной)</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -1012,7 +1016,11 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>за счётчиком, п. 12.9</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1020,7 +1028,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Регулятор давления «после себя» Ду 32, настройка 4,0 бар, с манометром</t>
+          <t>Фильтр тонкой очистки самопромывной Ду 32, 100 мкм, с манометром</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -1047,7 +1055,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Гребёнка (коллектор) Ду 32 на 10 выходов с шаровыми кранами на выходах, латунь никелированная</t>
+          <t>Регулятор давления «после себя» Ду 32, настройка 4,0 бар, с манометром</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1066,11 +1074,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>КХ, топочная 1.6; КХ-4 — ШВК-2, КХ-10 — ШВК-1, КХ-8 — автополив, КХ-9 — кухня</t>
-        </is>
-      </c>
+      <c r="I22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1078,7 +1082,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1¼" (В1) на 7 выходов ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
+          <t>Гребёнка (коллектор) Ду 32 на 10 выходов с шаровыми кранами на выходах, латунь никелированная</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1099,7 +1103,7 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>ШВК-2 (с/у 2.9, ниша); вход — КХ-4</t>
+          <t>КХ, топочная 1.6; КХ-4 — ШВК-2, КХ-10 — ШВК-1, КХ-8 — автополив, КХ-9 — кухня</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1113,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) на 6 выходов ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
+          <t>Коллектор распределительный 1¼" (В1) на 7 выходов ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1130,7 +1134,7 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>ШВК-2; Т4 — через Пс-2, Пс-1 к Н8</t>
+          <t>ШВК-2 (с/у 2.9, ниша); вход — КХ-4</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1144,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
+          <t>Коллектор распределительный 1" (Т3) на 6 выходов ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1161,7 +1165,7 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1 (с/у 1.4, ниша); вход — КХ-10</t>
+          <t>ШВК-2; Т4 — через Пс-2, Пс-1 к Н8</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
+          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1192,7 +1196,7 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1; Т4 — к Н8</t>
+          <t>ШВК-1 (с/у 1.4, ниша); вход — КХ-10</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1206,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) на 5 выходов ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
+          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1223,7 +1227,7 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б2 (баня, с/у б3, ниша); вход — Ecoflex, КЭ-2</t>
+          <t>ШВК-1; Т4 — к Н8</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1237,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный ¾" (Т3) на 2 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
+          <t>Коллектор распределительный 1" (В1) на 5 выходов ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1254,7 +1258,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б2; Т4 — через Пс-б1.1, б1.2, б2 к Н9</t>
+          <t>ШВК-Б2 (баня, с/у б3, ниша); вход — Ecoflex, КЭ-2</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
+          <t>Коллектор распределительный ¾" (Т3) на 2 выхода ¾" «евроконус» с шаровыми кранами (последний — Т4 с балансировочным клапаном), латунь никелированная</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1285,7 +1289,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б1 (баня, б7, ниша); вход — от подъёма Ecoflex, КЭ-3</t>
+          <t>ШВК-Б2; Т4 — через Пс-б1.1, б1.2, б2 к Н9</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1299,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (выход к Д-б1 — начало кольца Т3–Т4 через смесители Д-б1 и М-б1), латунь никелированная</t>
+          <t>Коллектор распределительный 1" (В1) на 3 выхода ¾" «евроконус» с шаровыми кранами, латунь никелированная</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1316,7 +1320,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б1; кольцо — к Н9</t>
+          <t>ШВК-Б1 (баня, б7, ниша); вход — от подъёма Ecoflex, КЭ-3</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1330,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Группа концевая коллектора: воздухоотводчик автоматический и кран спускной</t>
+          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (выход к Д-б1 — начало кольца Т3–Т4 через смесители Д-б1 и М-б1), латунь никелированная</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1338,16 +1342,16 @@
       <c r="E31" s="1" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>КХ, ШВК-1, ШВК-2, ШВК-Б1, ШВК-Б2</t>
+          <t>ШВК-Б1; кольцо — к Н9</t>
         </is>
       </c>
     </row>
@@ -1357,28 +1361,28 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встраиваемый ≈900×650×120 мм с монтажной рамой</t>
+          <t>Группа концевая коллектора: воздухоотводчик автоматический и кран спускной</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>ШРВ, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr"/>
       <c r="E32" s="1" t="inlineStr"/>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>ШВК-2, ниша перегородки 2.9/2.8</t>
+          <t>КХ, ШВК-1, ШВК-2, ШВК-Б1, ШВК-Б2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1392,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встраиваемый ≈750×600×120 мм с монтажной рамой</t>
+          <t>Шкаф коллекторный встраиваемый ≈900×650×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1409,7 +1413,7 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1, ниша стены 1.4/1.3</t>
+          <t>ШВК-2, ниша перегородки 2.9/2.8</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1423,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встраиваемый ≈700×600×120 мм с монтажной рамой</t>
+          <t>Шкаф коллекторный встраиваемый ≈750×600×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1440,7 +1444,7 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б2, ниша перегородки б3/б4</t>
+          <t>ШВК-1, ниша стены 1.4/1.3</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1454,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встраиваемый ≈820×650×120 мм с монтажной рамой</t>
+          <t>Шкаф коллекторный встраиваемый ≈700×600×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1471,7 +1475,7 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>ШВК-Б1, ниша в восточной стене б7 у южного угла</t>
+          <t>ШВК-Б2, ниша перегородки б3/б4</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1485,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Люк нажимной скрытый под плитку (алюминиевая рама, дверца под облицовку) по размеру ниши шкафа</t>
+          <t>Шкаф коллекторный встраиваемый ≈820×650×120 мм с монтажной рамой</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ШРВ, или аналог</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr"/>
@@ -1497,12 +1501,12 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>ШВК-1 (1.4), ШВК-2 (2.9), ШВК-Б2 (б3), ШВК-Б1 (б7)</t>
+          <t>ШВК-Б1, ниша в восточной стене б7 у южного угла</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1516,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Поддон под коллекторный шкаф с отбортовкой</t>
+          <t>Люк нажимной скрытый под плитку (алюминиевая рама, дверца под облицовку) по размеру ниши шкафа</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1533,55 +1537,55 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>датчики ДП под шкафами (лист 14, узел 10)</t>
+          <t>ШВК-1 (1.4), ШВК-2 (2.9), ШВК-Б2 (б3), ШВК-Б1 (б7)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Поддон под коллекторный шкаф с отбортовкой</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr"/>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>датчики ДП под шкафами (лист 14, узел 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>3. Трубопроводы (по 3D-модели)</t>
         </is>
       </c>
-      <c r="C38" s="1" t="n"/>
-      <c r="D38" s="1" t="n"/>
-      <c r="E38" s="1" t="n"/>
-      <c r="F38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="1" t="n"/>
-      <c r="I38" s="1" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Труба напорная ПЭ 100 SDR11 32×3,0 питьевая</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 18599-2001</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr">
-        <is>
-          <t>ввод: под краем плиты и сквозь плиту в футляре до перехода на PE-Xa (+0,45); по модели 2,5 м</t>
-        </is>
-      </c>
+      <c r="C39" s="1" t="n"/>
+      <c r="D39" s="1" t="n"/>
+      <c r="E39" s="1" t="n"/>
+      <c r="F39" s="1" t="n"/>
+      <c r="G39" s="1" t="n"/>
+      <c r="H39" s="1" t="n"/>
+      <c r="I39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1589,12 +1593,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 32×4,4, класс 2 и ХВ, 10 бар</t>
+          <t>Труба напорная ПЭ 100 SDR11 32×3,0 питьевая</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32415-2013, или аналог</t>
+          <t>ГОСТ 18599-2001</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr"/>
@@ -1605,12 +1609,12 @@
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 10,2 м + 10 %</t>
+          <t>ввод: под краем плиты и сквозь плиту в футляре до перехода на PE-Xa (+0,45); по модели 2,5 м</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1624,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 25×3,5, класс 2 и ХВ, 10 бар</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 32×4,4, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1636,12 +1640,12 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 69,5, Т3 41,9 м + 10 %</t>
+          <t>по модели В1 10,2 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 20×2,8, класс 2 и ХВ, 10 бар</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 25×3,5, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1667,12 +1671,12 @@
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>186</v>
+        <v>123</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 37,9, Т3 63,7, Т4 67,0 м + 10 %</t>
+          <t>по модели В1 69,5, Т3 41,9 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1686,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Труба из сшитого полиэтилена PE-Xa 16×2,2, класс 2 и ХВ, 10 бар</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 20×2,8, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1698,12 +1702,12 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 69,6, Т3 24,7 м + 10 %</t>
+          <t>по модели В1 37,9, Т3 63,7, Т4 67,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1717,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Труба канализационная малошумная трёхслойная Ø110 (ПП с минеральным наполнителем)</t>
+          <t>Труба из сшитого полиэтилена PE-Xa 16×2,2, класс 2 и ХВ, 10 бар</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
+          <t>ГОСТ 32415-2013, или аналог</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr"/>
@@ -1729,12 +1733,12 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 26,9 м</t>
+          <t>по модели В1 69,6, Т3 24,7 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1748,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Труба канализационная малошумная трёхслойная Ø50 (ПП с минеральным наполнителем)</t>
+          <t>Труба канализационная малошумная трёхслойная Ø110 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1760,12 +1764,12 @@
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 24,2 м</t>
+          <t>внутри зданий; по модели 26,9 м</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1779,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Труба канализационная малошумная трёхслойная Ø32 (ПП с минеральным наполнителем)</t>
+          <t>Труба канализационная малошумная трёхслойная Ø50 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1791,12 +1795,12 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 0,6 м</t>
+          <t>внутри зданий; по модели 24,2 м</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1810,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
+          <t>Труба канализационная малошумная трёхслойная Ø32 (ПП с минеральным наполнителем)</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; Skolan dB, Raupiano Plus или аналог</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr"/>
@@ -1822,12 +1826,12 @@
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 26,1 м</t>
+          <t>внутри зданий; по модели 0,6 м</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1841,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
+          <t>Труба полипропиленовая канализационная Ø50×1,8 — в грунте под плитой</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr"/>
@@ -1853,12 +1857,12 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>сборные под плитой и выпуски; по модели 42,3 м + выводы прочисток до +0,200 (3 шт.) 4,2 м</t>
+          <t>отводы в песчаной обсыпке; по модели 26,1 м</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1872,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная наружная Ø110, SN8 — К2 от пескоуловителя гаража</t>
+          <t>Труба полипропиленовая канализационная наружная Ø110, SN8</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1884,12 +1888,12 @@
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>К2-1 (лист 4); по модели 2,1 м, отвод 2 × 45° — по месту</t>
+          <t>сборные под плитой и выпуски; по модели 42,3 м + выводы прочисток до +0,200 (3 шт.) 4,2 м</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1903,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
+          <t>Труба полипропиленовая канализационная наружная Ø110, SN8 — К2 от пескоуловителя гаража</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1911,16 +1915,16 @@
       <c r="E50" s="1" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>К1-1 — выпуск (юг) и ввод линии бани (север); баня — выпуски К1-б и К1-бв; К2-1 (лист 14, узел 2)</t>
+          <t>К2-1 (лист 4); по модели 2,1 м, отвод 2 × 45° — по месту</t>
         </is>
       </c>
     </row>
@@ -1930,28 +1934,28 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Футляр из трубы ПЭ 100 SDR17 75×4,5 (техническая) — ввод без приямка: под краем плиты и сквозь плиту, закладывается до бетонирования</t>
+          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 18599-2001</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr"/>
       <c r="E51" s="1" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>ввод В1 2,1 м, КХ-8 2,5 м по оси, от 0,15 м за наружной гранью до +0,03 (лист 14, узел 1; ТЗ-1)</t>
+          <t>К1-1 — выпуск (юг) и ввод линии бани (север); баня — выпуски К1-б и К1-бв; К2-1 (лист 14, узел 2)</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1965,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПЭ Ø75, 90°, радиус по оси не менее 0,3 м (≥ 8 d трубы в футляре) — гнутый или сварной</t>
+          <t>Футляр из трубы ПЭ 100 SDR17 75×4,5 (техническая) — ввод без приямка: под краем плиты и сквозь плиту, закладывается до бетонирования</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1973,64 +1977,64 @@
       <c r="E52" s="1" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
+          <t>ввод В1 2,1 м, КХ-8 2,5 м по оси, от 0,15 м за наружной гранью до +0,03 (лист 14, узел 1; ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПЭ Ø75, 90°, радиус по оси не менее 0,3 м (≥ 8 d трубы в футляре) — гнутый или сварной</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 18599-2001</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
           <t>ввод В1 — 1, КХ-8 — 2; трубу можно вынуть без вскрытия плиты</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr"/>
-      <c r="B53" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>4. Фасонные части (подсчёт по 3D-модели)</t>
         </is>
       </c>
-      <c r="C53" s="1" t="n"/>
-      <c r="D53" s="1" t="n"/>
-      <c r="E53" s="1" t="n"/>
-      <c r="F53" s="1" t="n"/>
-      <c r="G53" s="1" t="n"/>
-      <c r="H53" s="1" t="n"/>
-      <c r="I53" s="1" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>выходы коллекторов</t>
-        </is>
-      </c>
+      <c r="C54" s="1" t="n"/>
+      <c r="D54" s="1" t="n"/>
+      <c r="E54" s="1" t="n"/>
+      <c r="F54" s="1" t="n"/>
+      <c r="G54" s="1" t="n"/>
+      <c r="H54" s="1" t="n"/>
+      <c r="I54" s="1" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -2038,7 +2042,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2054,7 +2058,7 @@
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2085,7 +2089,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
@@ -2100,7 +2104,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2116,12 +2120,12 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2135,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2147,12 +2151,12 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2166,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2178,12 +2182,12 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2197,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2209,7 +2213,7 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
@@ -2224,7 +2228,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
+          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2240,12 +2244,12 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2259,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2271,7 +2275,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
@@ -2286,7 +2290,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 25×3,5</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 20×2,8</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2302,7 +2306,7 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
@@ -2317,7 +2321,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 25×3,5</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2348,7 +2352,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2379,7 +2383,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 25×3,5</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 20×2,8</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2395,7 +2399,7 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
@@ -2410,7 +2414,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 25×3,5</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2426,12 +2430,12 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2445,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2457,7 +2461,7 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
@@ -2472,7 +2476,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2488,7 +2492,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
@@ -2503,7 +2507,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2519,7 +2523,7 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
@@ -2534,7 +2538,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2550,12 +2554,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>в 1.6 над полом (+0,45), под краном на вводе (лист 7; лист 14, узел 1)</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2577,7 +2581,7 @@
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G72" s="1" t="n">
@@ -2586,7 +2590,7 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>в 1.6 над полом (+0,45), под краном на вводе (лист 7; лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2596,28 +2600,28 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø110, 45°</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>повороты и низ подъёмов по модели</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2631,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 45°</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2643,7 +2647,7 @@
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
@@ -2658,7 +2662,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 30°</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2674,7 +2678,7 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
@@ -2689,7 +2693,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 45°</t>
+          <t>Отвод канализационный малошумный Ø50, 30°</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2705,7 +2709,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
@@ -2720,7 +2724,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 30°</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2751,7 +2755,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
+          <t>Отвод канализационный малошумный Ø32, 30°</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2767,12 +2771,12 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты и низ подъёмов по модели</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2786,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2798,7 +2802,7 @@
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
@@ -2813,7 +2817,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2829,7 +2833,7 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
@@ -2844,12 +2848,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr"/>
@@ -2860,12 +2864,12 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>повороты, низ подъёмов и стояков по модели, прочистки</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2879,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 15°</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2891,12 +2895,12 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>К1-б: поворот 60° в б6 — 45° + 15°</t>
+          <t>повороты, низ подъёмов и стояков по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Отвод ПП канализационный Ø110, 15°</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2922,12 +2926,12 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>повороты, низ подъёмов и стояков по модели</t>
+          <t>К1-б: поворот 60° в б6 — 45° + 15°</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2941,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 30°</t>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2953,12 +2957,12 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>К1-М-б1 у стояка</t>
+          <t>повороты, низ подъёмов и стояков по модели</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2972,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Отвод ПП канализационный Ø50, 30°</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2984,12 +2988,12 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>К1-М-б1 у стояка</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3003,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -3015,7 +3019,7 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
@@ -3030,7 +3034,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3046,7 +3050,7 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
@@ -3061,7 +3065,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3082,7 +3086,7 @@
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>б6, 1.8, 1.9</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3096,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3108,12 +3112,12 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
+          <t>б6, 1.8, 1.9</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3127,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr"/>
@@ -3139,12 +3143,12 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
+          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3158,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr"/>
@@ -3175,7 +3179,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3189,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3197,64 +3201,64 @@
       <c r="E92" s="1" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
+          <t>прочистки в грунте</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr"/>
+      <c r="E93" s="1" t="inlineStr"/>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="1" t="inlineStr"/>
+      <c r="I93" s="1" t="inlineStr">
+        <is>
           <t>по месту</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="3" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
         </is>
       </c>
-      <c r="C93" s="1" t="n"/>
-      <c r="D93" s="1" t="n"/>
-      <c r="E93" s="1" t="n"/>
-      <c r="F93" s="1" t="n"/>
-      <c r="G93" s="1" t="n"/>
-      <c r="H93" s="1" t="n"/>
-      <c r="I93" s="1" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr"/>
-      <c r="E94" s="1" t="inlineStr"/>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr">
-        <is>
-          <t>вход В1 в ШВК-2</t>
-        </is>
-      </c>
+      <c r="C94" s="1" t="n"/>
+      <c r="D94" s="1" t="n"/>
+      <c r="E94" s="1" t="n"/>
+      <c r="F94" s="1" t="n"/>
+      <c r="G94" s="1" t="n"/>
+      <c r="H94" s="1" t="n"/>
+      <c r="I94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -3262,7 +3266,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3278,12 +3282,12 @@
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
+          <t>вход В1 в ШВК-2</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3297,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3309,12 +3313,12 @@
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
+          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3328,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3340,12 +3344,12 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3359,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3371,12 +3375,12 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>на Т4 у Н8, Н9</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -3407,7 +3411,7 @@
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3421,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -3438,7 +3442,7 @@
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3452,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3464,12 +3468,12 @@
         </is>
       </c>
       <c r="G101" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3483,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Arrowhead 485 или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr"/>
@@ -3495,12 +3499,12 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
+          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
         </is>
       </c>
     </row>
@@ -3510,12 +3514,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Arrowhead 485 или аналог</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr"/>
@@ -3526,12 +3530,12 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3545,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3557,60 +3561,60 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
+          <t>СМ-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr"/>
+      <c r="E105" s="1" t="inlineStr"/>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H105" s="1" t="inlineStr"/>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
           <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr"/>
-      <c r="B105" s="3" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr"/>
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>6. Санитарные приборы и изделия канализации</t>
         </is>
       </c>
-      <c r="C105" s="1" t="n"/>
-      <c r="D105" s="1" t="n"/>
-      <c r="E105" s="1" t="n"/>
-      <c r="F105" s="1" t="n"/>
-      <c r="G105" s="1" t="n"/>
-      <c r="H105" s="1" t="n"/>
-      <c r="I105" s="1" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>по дизайн-проекту</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr"/>
-      <c r="E106" s="1" t="inlineStr"/>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
-        </is>
-      </c>
+      <c r="C106" s="1" t="n"/>
+      <c r="D106" s="1" t="n"/>
+      <c r="E106" s="1" t="n"/>
+      <c r="F106" s="1" t="n"/>
+      <c r="G106" s="1" t="n"/>
+      <c r="H106" s="1" t="n"/>
+      <c r="I106" s="1" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -3618,7 +3622,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3634,12 +3638,12 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-4, УМ-б1</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3653,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3665,12 +3669,12 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3684,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3701,7 +3705,7 @@
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3727,12 +3731,12 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3746,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3754,16 +3758,16 @@
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3777,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
@@ -3789,12 +3793,12 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3808,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3820,12 +3824,12 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3839,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3856,7 +3860,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3870,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3887,7 +3891,7 @@
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3901,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3913,12 +3917,12 @@
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3932,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3944,12 +3948,12 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3963,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3980,7 +3984,7 @@
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3994,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -4011,7 +4015,7 @@
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4025,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr"/>
@@ -4037,12 +4041,12 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4056,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr"/>
@@ -4068,12 +4072,12 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4087,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4095,16 +4099,16 @@
       <c r="E122" s="1" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4118,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4126,64 +4130,64 @@
       <c r="E123" s="1" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr"/>
+      <c r="E124" s="1" t="inlineStr"/>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="1" t="inlineStr"/>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
           <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="1" t="inlineStr"/>
-      <c r="B124" s="3" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr"/>
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
         </is>
       </c>
-      <c r="C124" s="1" t="n"/>
-      <c r="D124" s="1" t="n"/>
-      <c r="E124" s="1" t="n"/>
-      <c r="F124" s="1" t="n"/>
-      <c r="G124" s="1" t="n"/>
-      <c r="H124" s="1" t="n"/>
-      <c r="I124" s="1" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>Neptun, Аквасторож, или аналог</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr"/>
-      <c r="E125" s="1" t="inlineStr"/>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
-        </is>
-      </c>
+      <c r="C125" s="1" t="n"/>
+      <c r="D125" s="1" t="n"/>
+      <c r="E125" s="1" t="n"/>
+      <c r="F125" s="1" t="n"/>
+      <c r="G125" s="1" t="n"/>
+      <c r="H125" s="1" t="n"/>
+      <c r="I125" s="1" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -4191,12 +4195,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Neptun, Аквасторож, или аналог</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr"/>
@@ -4207,12 +4211,12 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4226,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -4238,12 +4242,12 @@
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4257,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr"/>
@@ -4269,12 +4273,12 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-19</t>
+          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4288,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -4296,64 +4300,64 @@
       <c r="E129" s="1" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
+          <t>ДП-1…ДП-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Кабель-удлинитель датчиков (системный)</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>той же системы</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr"/>
+      <c r="E130" s="1" t="inlineStr"/>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="H130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
           <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr"/>
-      <c r="B130" s="3" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr"/>
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>8. Изоляция, гильзы и крепления</t>
         </is>
       </c>
-      <c r="C130" s="1" t="n"/>
-      <c r="D130" s="1" t="n"/>
-      <c r="E130" s="1" t="n"/>
-      <c r="F130" s="1" t="n"/>
-      <c r="G130" s="1" t="n"/>
-      <c r="H130" s="1" t="n"/>
-      <c r="I130" s="1" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr"/>
-      <c r="E131" s="1" t="inlineStr"/>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="C131" s="1" t="n"/>
+      <c r="D131" s="1" t="n"/>
+      <c r="E131" s="1" t="n"/>
+      <c r="F131" s="1" t="n"/>
+      <c r="G131" s="1" t="n"/>
+      <c r="H131" s="1" t="n"/>
+      <c r="I131" s="1" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -4361,7 +4365,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -4377,7 +4381,7 @@
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
@@ -4392,7 +4396,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -4408,7 +4412,7 @@
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
@@ -4423,7 +4427,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -4439,7 +4443,7 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
@@ -4454,7 +4458,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4470,7 +4474,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
@@ -4485,7 +4489,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4501,7 +4505,7 @@
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
@@ -4516,7 +4520,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4532,7 +4536,7 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
@@ -4547,7 +4551,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4563,12 +4567,12 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4582,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4594,7 +4598,7 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
@@ -4609,28 +4613,28 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr"/>
       <c r="E140" s="1" t="inlineStr"/>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4644,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4656,12 +4660,12 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 20, стены 9 (ТЗ-1, лист 4; лист 14)</t>
+          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4675,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -4687,12 +4691,12 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
+          <t>плиты и перекрытия 20, стены 9 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4702,28 +4706,28 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr"/>
       <c r="E143" s="1" t="inlineStr"/>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4737,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -4749,12 +4753,12 @@
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4768,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
+          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -4780,12 +4784,12 @@
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>3 проёма (ТЗ-1, лист 4)</t>
+          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4799,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -4807,16 +4811,16 @@
       <c r="E146" s="1" t="inlineStr"/>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>лист 6; НВК — так же во дворе</t>
+          <t>3 проёма (ТЗ-1, лист 4)</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
+          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -4842,12 +4846,12 @@
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
+          <t>лист 6; НВК — так же во дворе</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4861,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -4869,16 +4873,16 @@
       <c r="E148" s="1" t="inlineStr"/>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>36</v>
+        <v>3.1</v>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4892,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -4904,7 +4908,7 @@
         </is>
       </c>
       <c r="G149" s="1" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr">
@@ -4919,7 +4923,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -4935,7 +4939,7 @@
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr">
@@ -4950,7 +4954,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -4966,7 +4970,7 @@
         </is>
       </c>
       <c r="G151" s="1" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr">
@@ -4981,7 +4985,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -4997,7 +5001,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr">
@@ -5012,7 +5016,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -5028,7 +5032,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr">
@@ -5043,7 +5047,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -5059,7 +5063,7 @@
         </is>
       </c>
       <c r="G154" s="1" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr">
@@ -5074,7 +5078,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -5090,46 +5094,60 @@
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>650</v>
+        <v>39</v>
       </c>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr">
         <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr"/>
+      <c r="E156" s="1" t="inlineStr"/>
+      <c r="F156" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>650</v>
+      </c>
+      <c r="H156" s="1" t="inlineStr"/>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
           <t>шаг 0,5 м</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="1" t="inlineStr"/>
-      <c r="B156" s="3" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr"/>
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>9. Не входит в ВК.СО</t>
         </is>
       </c>
-      <c r="C156" s="1" t="n"/>
-      <c r="D156" s="1" t="n"/>
-      <c r="E156" s="1" t="n"/>
-      <c r="F156" s="1" t="n"/>
-      <c r="G156" s="1" t="n"/>
-      <c r="H156" s="1" t="n"/>
-      <c r="I156" s="1" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>146</v>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C157" s="1" t="inlineStr"/>
-      <c r="D157" s="1" t="inlineStr"/>
-      <c r="E157" s="1" t="inlineStr"/>
-      <c r="F157" s="1" t="inlineStr"/>
-      <c r="G157" s="1" t="inlineStr"/>
-      <c r="H157" s="1" t="inlineStr"/>
-      <c r="I157" s="1" t="inlineStr"/>
+      <c r="C157" s="1" t="n"/>
+      <c r="D157" s="1" t="n"/>
+      <c r="E157" s="1" t="n"/>
+      <c r="F157" s="1" t="n"/>
+      <c r="G157" s="1" t="n"/>
+      <c r="H157" s="1" t="n"/>
+      <c r="I157" s="1" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -5137,7 +5155,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr"/>
@@ -5154,7 +5172,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr"/>
@@ -5171,7 +5189,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr"/>
@@ -5188,7 +5206,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr"/>
@@ -5205,7 +5223,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr"/>
@@ -5216,9 +5234,26 @@
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr"/>
+      <c r="D163" s="1" t="inlineStr"/>
+      <c r="E163" s="1" t="inlineStr"/>
+      <c r="F163" s="1" t="inlineStr"/>
+      <c r="G163" s="1" t="inlineStr"/>
+      <c r="H163" s="1" t="inlineStr"/>
+      <c r="I163" s="1" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1676,7 +1676,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 69,5, Т3 41,9 м + 10 %</t>
+          <t>по модели В1 69,5, Т3 42,0 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 37,9, Т3 63,7, Т4 67,0 м + 10 %</t>
+          <t>по модели В1 37,9, Т3 63,7, Т4 67,1 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 69,6, Т3 24,7 м + 10 %</t>
+          <t>по модели В1 70,6, Т3 25,2 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>внутри зданий; по модели 24,2 м</t>
+          <t>внутри зданий; по модели 24,5 м</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>отводы в песчаной обсыпке; по модели 26,1 м</t>
+          <t>отводы в песчаной обсыпке; по модели 22,3 м</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Крестовина канализационная малошумная косая 45° Ø50×50×50</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2869,7 +2869,7 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>пол 1.4: УМ-1, Д-1, сифон конденсата → Ст.К1-2</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr"/>
@@ -2895,12 +2895,12 @@
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>повороты, низ подъёмов и стояков по модели, прочистки</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 15°</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2926,12 +2926,12 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>К1-б: поворот 60° в б6 — 45° + 15°</t>
+          <t>повороты, низ подъёмов и стояков по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Отвод ПП канализационный Ø110, 15°</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2957,12 +2957,12 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>повороты, низ подъёмов и стояков по модели</t>
+          <t>К1-б: поворот 60° в б6 — 45° + 15°</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 30°</t>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2988,12 +2988,12 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>К1-М-б1 у стояка</t>
+          <t>повороты, низ подъёмов и стояков по модели</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Отвод ПП канализационный Ø50, 30°</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -3019,12 +3019,12 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>К1-М-б1 у стояка</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник ПП канализационный 87,5° Ø110×50</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3081,12 +3081,12 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>на выводе прочистки Ст.К1-2 — отвод Ø50 из пола 1.4</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3112,12 +3112,12 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>б6, 1.8, 1.9</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -3143,12 +3143,12 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr"/>
@@ -3179,7 +3179,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
+          <t>б6, 1.8, 1.9</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3205,12 +3205,12 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
         </is>
       </c>
     </row>
@@ -3220,65 +3220,81 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr"/>
       <c r="E93" s="1" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr"/>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="n"/>
-      <c r="D94" s="1" t="n"/>
-      <c r="E94" s="1" t="n"/>
-      <c r="F94" s="1" t="n"/>
-      <c r="G94" s="1" t="n"/>
-      <c r="H94" s="1" t="n"/>
-      <c r="I94" s="1" t="n"/>
+      <c r="A94" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 32414-2013</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr"/>
+      <c r="E94" s="1" t="inlineStr"/>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H94" s="1" t="inlineStr"/>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>прочистки в грунте</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr"/>
       <c r="E95" s="1" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G95" s="1" t="n">
@@ -3287,40 +3303,24 @@
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>вход В1 в ШВК-2</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr"/>
-      <c r="E96" s="1" t="inlineStr"/>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G96" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr">
-        <is>
-          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
-        </is>
-      </c>
+      <c r="A96" s="1" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n"/>
+      <c r="D96" s="1" t="n"/>
+      <c r="E96" s="1" t="n"/>
+      <c r="F96" s="1" t="n"/>
+      <c r="G96" s="1" t="n"/>
+      <c r="H96" s="1" t="n"/>
+      <c r="I96" s="1" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3344,12 +3344,12 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
+          <t>вход В1 в ШВК-2</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3375,12 +3375,12 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9</t>
+          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -3406,12 +3406,12 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, подводка автополива</t>
+          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -3437,12 +3437,12 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>на Т4 у Н8, Н9 и на Т4 каждого кольца — рядом с балансировочным клапаном (против противотока)</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3473,7 +3473,7 @@
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3499,12 +3499,12 @@
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Arrowhead 485 или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr"/>
@@ -3530,12 +3530,12 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
+          <t>КХ-8, за наружной гранью фундамента</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3561,12 +3561,12 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Arrowhead 485 или аналог</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr"/>
@@ -3592,91 +3592,91 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
+          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="inlineStr"/>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="n"/>
-      <c r="D106" s="1" t="n"/>
-      <c r="E106" s="1" t="n"/>
-      <c r="F106" s="1" t="n"/>
-      <c r="G106" s="1" t="n"/>
-      <c r="H106" s="1" t="n"/>
-      <c r="I106" s="1" t="n"/>
+      <c r="A106" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr"/>
+      <c r="E106" s="1" t="inlineStr"/>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="inlineStr"/>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>СМ-1</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr"/>
       <c r="E107" s="1" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Умывальник со смесителем и сифоном</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>по дизайн-проекту</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr"/>
-      <c r="E108" s="1" t="inlineStr"/>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>УМ-1…УМ-4, УМ-б1</t>
-        </is>
-      </c>
+      <c r="A108" s="1" t="inlineStr"/>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n"/>
+      <c r="D108" s="1" t="n"/>
+      <c r="E108" s="1" t="n"/>
+      <c r="F108" s="1" t="n"/>
+      <c r="G108" s="1" t="n"/>
+      <c r="H108" s="1" t="n"/>
+      <c r="I108" s="1" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3700,12 +3700,12 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3731,12 +3731,12 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3762,12 +3762,12 @@
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>М-1, М-б1</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -3789,16 +3789,16 @@
       <c r="E112" s="1" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3808,19 +3808,19 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr"/>
       <c r="E113" s="1" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G113" s="1" t="n">
@@ -3829,7 +3829,7 @@
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr"/>
@@ -3860,7 +3860,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3886,12 +3886,12 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3922,7 +3922,7 @@
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3948,12 +3948,12 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3984,7 +3984,7 @@
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -4010,12 +4010,12 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -4046,7 +4046,7 @@
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr"/>
@@ -4072,12 +4072,12 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
+          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4103,12 +4103,12 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
+          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
         </is>
       </c>
     </row>
@@ -4118,28 +4118,28 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr"/>
       <c r="E123" s="1" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -4165,42 +4165,58 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>ПУ-1, гараж (лист 4)</t>
+          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="n"/>
-      <c r="D125" s="1" t="n"/>
-      <c r="E125" s="1" t="n"/>
-      <c r="F125" s="1" t="n"/>
-      <c r="G125" s="1" t="n"/>
-      <c r="H125" s="1" t="n"/>
-      <c r="I125" s="1" t="n"/>
+      <c r="A125" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr"/>
+      <c r="E125" s="1" t="inlineStr"/>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H125" s="1" t="inlineStr"/>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Neptun, Аквасторож, или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr"/>
@@ -4211,45 +4227,29 @@
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
+          <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D127" s="1" t="inlineStr"/>
-      <c r="E127" s="1" t="inlineStr"/>
-      <c r="F127" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G127" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H127" s="1" t="inlineStr"/>
-      <c r="I127" s="1" t="inlineStr">
-        <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
-        </is>
-      </c>
+      <c r="A127" s="1" t="inlineStr"/>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n"/>
+      <c r="D127" s="1" t="n"/>
+      <c r="E127" s="1" t="n"/>
+      <c r="F127" s="1" t="n"/>
+      <c r="G127" s="1" t="n"/>
+      <c r="H127" s="1" t="n"/>
+      <c r="I127" s="1" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Neptun, Аквасторож, или аналог</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr"/>
@@ -4278,7 +4278,7 @@
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr"/>
@@ -4304,12 +4304,12 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-19</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
@@ -4319,58 +4319,74 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr"/>
       <c r="E130" s="1" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>оценка по плану; прокладка — ЭОМ/СС</t>
+          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr"/>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>8. Изоляция, гильзы и крепления</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="n"/>
-      <c r="D131" s="1" t="n"/>
-      <c r="E131" s="1" t="n"/>
-      <c r="F131" s="1" t="n"/>
-      <c r="G131" s="1" t="n"/>
-      <c r="H131" s="1" t="n"/>
-      <c r="I131" s="1" t="n"/>
+      <c r="A131" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Датчик протечки проводной напольный</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>той же системы</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr"/>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>ДП-1…ДП-19</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
+          <t>Кабель-удлинитель датчиков (системный)</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr"/>
@@ -4381,45 +4397,29 @@
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>123</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr"/>
-      <c r="E133" s="1" t="inlineStr"/>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="H133" s="1" t="inlineStr"/>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="A133" s="1" t="inlineStr"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>8. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n"/>
+      <c r="D133" s="1" t="n"/>
+      <c r="E133" s="1" t="n"/>
+      <c r="F133" s="1" t="n"/>
+      <c r="G133" s="1" t="n"/>
+      <c r="H133" s="1" t="n"/>
+      <c r="I133" s="1" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4598,12 +4598,12 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -4629,12 +4629,12 @@
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4644,28 +4644,28 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr"/>
       <c r="E141" s="1" t="inlineStr"/>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4675,28 +4675,28 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr"/>
       <c r="E142" s="1" t="inlineStr"/>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 20, стены 9 (ТЗ-1, лист 4; лист 14)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -4722,12 +4722,12 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
+          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4737,28 +4737,28 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr"/>
       <c r="E144" s="1" t="inlineStr"/>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>плиты и перекрытия 17, стены 9 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4768,28 +4768,28 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr"/>
       <c r="E145" s="1" t="inlineStr"/>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
+          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -4820,7 +4820,7 @@
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>3 проёма (ТЗ-1, лист 4)</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
+          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -4842,16 +4842,16 @@
       <c r="E147" s="1" t="inlineStr"/>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>лист 6; НВК — так же во дворе</t>
+          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -4873,16 +4873,16 @@
       <c r="E148" s="1" t="inlineStr"/>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
+          <t>3 проёма (ТЗ-1, лист 4)</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -4904,16 +4904,16 @@
       <c r="E149" s="1" t="inlineStr"/>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G149" s="1" t="n">
-        <v>36</v>
+        <v>2.4</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>лист 6; НВК — так же во дворе</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -4935,16 +4935,16 @@
       <c r="E150" s="1" t="inlineStr"/>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>81</v>
+        <v>3.1</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="G151" s="1" t="n">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="G154" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -5125,63 +5125,91 @@
         </is>
       </c>
       <c r="G156" s="1" t="n">
-        <v>650</v>
+        <v>2</v>
       </c>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr">
         <is>
-          <t>шаг 0,5 м</t>
+          <t>шаг — лист 14</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="inlineStr"/>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>9. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C157" s="1" t="n"/>
-      <c r="D157" s="1" t="n"/>
-      <c r="E157" s="1" t="n"/>
-      <c r="F157" s="1" t="n"/>
-      <c r="G157" s="1" t="n"/>
-      <c r="H157" s="1" t="n"/>
-      <c r="I157" s="1" t="n"/>
+      <c r="A157" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr"/>
+      <c r="E157" s="1" t="inlineStr"/>
+      <c r="F157" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G157" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="H157" s="1" t="inlineStr"/>
+      <c r="I157" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C158" s="1" t="inlineStr"/>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D158" s="1" t="inlineStr"/>
       <c r="E158" s="1" t="inlineStr"/>
-      <c r="F158" s="1" t="inlineStr"/>
-      <c r="G158" s="1" t="inlineStr"/>
+      <c r="F158" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>650</v>
+      </c>
       <c r="H158" s="1" t="inlineStr"/>
-      <c r="I158" s="1" t="inlineStr"/>
+      <c r="I158" s="1" t="inlineStr">
+        <is>
+          <t>шаг 0,5 м</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
-        </is>
-      </c>
-      <c r="C159" s="1" t="inlineStr"/>
-      <c r="D159" s="1" t="inlineStr"/>
-      <c r="E159" s="1" t="inlineStr"/>
-      <c r="F159" s="1" t="inlineStr"/>
-      <c r="G159" s="1" t="inlineStr"/>
-      <c r="H159" s="1" t="inlineStr"/>
-      <c r="I159" s="1" t="inlineStr"/>
+      <c r="A159" s="1" t="inlineStr"/>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>9. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="n"/>
+      <c r="D159" s="1" t="n"/>
+      <c r="E159" s="1" t="n"/>
+      <c r="F159" s="1" t="n"/>
+      <c r="G159" s="1" t="n"/>
+      <c r="H159" s="1" t="n"/>
+      <c r="I159" s="1" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -5189,7 +5217,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr"/>
@@ -5206,7 +5234,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr"/>
@@ -5223,7 +5251,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr"/>
@@ -5240,7 +5268,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr"/>
@@ -5251,9 +5279,43 @@
       <c r="H163" s="1" t="inlineStr"/>
       <c r="I163" s="1" t="inlineStr"/>
     </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr"/>
+      <c r="D164" s="1" t="inlineStr"/>
+      <c r="E164" s="1" t="inlineStr"/>
+      <c r="F164" s="1" t="inlineStr"/>
+      <c r="G164" s="1" t="inlineStr"/>
+      <c r="H164" s="1" t="inlineStr"/>
+      <c r="I164" s="1" t="inlineStr"/>
+    </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr">
+      <c r="A165" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr"/>
+      <c r="D165" s="1" t="inlineStr"/>
+      <c r="E165" s="1" t="inlineStr"/>
+      <c r="F165" s="1" t="inlineStr"/>
+      <c r="G165" s="1" t="inlineStr"/>
+      <c r="H165" s="1" t="inlineStr"/>
+      <c r="I165" s="1" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный для ГВС Н9 (баня), то же, Q = 0,24 м³/ч, H = 0,7 м</t>
+          <t>Насос циркуляционный для ГВС Н9 (баня), то же, Q = 0,27 м³/ч, H = 0,7 м</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (выход к Д-б1 — начало кольца Т3–Т4 через смесители Д-б1 и М-б1), латунь никелированная</t>
+          <t>Коллектор распределительный 1" (Т3) на 3 выхода ¾" «евроконус» с шаровыми кранами (выход к Д-б1 — начало кольца Т3–Т4 через смеситель Д-б1), латунь никелированная</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1702,12 +1702,12 @@
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>по модели В1 37,9, Т3 63,7, Т4 67,1 м + 10 %</t>
+          <t>по модели В1 37,9, Т3 56,3, Т4 83,5 м + 10 %</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
@@ -3406,12 +3406,12 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, к смесителю Д-б1 (тройник кольца), к смесителю М-б1 (тройник кольца), Т4 кольца ШВК-Б1 у Н9</t>
+          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, В1 мойки М-б1 под мойкой, к смесителю Д-б1 (тройник кольца), Т3 кухни бани — у Б2 и к смесителю мойки М-б1 — 2, Т4 кухни бани и кольца ШВК-Б1 у Н9</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
@@ -3561,12 +3561,12 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, ШВК-Б2 (П4)</t>
+          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, кухня бани — под мойкой М-б1, ШВК-Б2 (П4)</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr">

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1934,28 +1934,28 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
+          <t>Труба чугунная безраструбная SML DN100 (наружный Ø110), внутри — эпоксидное покрытие, снаружи — грунтовка</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32413-2013</t>
+          <t>EN 877; Smart SML или аналог</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr"/>
       <c r="E51" s="1" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>К1-1 — выпуск (юг) и ввод линии бани (север); баня — выпуски К1-б и К1-бв; К2-1 (лист 14, узел 2)</t>
+          <t>водостоки К2 в стенах (лист 15): стояки Ст.К2-1…8 53,3 м и выпуски к ДК 5,6 м по модели + 10 %</t>
         </is>
       </c>
     </row>
@@ -1965,28 +1965,28 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Футляр из трубы ПЭ 100 SDR17 75×4,5 (техническая) — ввод без приямка: под краем плиты и сквозь плиту, закладывается до бетонирования</t>
+          <t>Футляр из трубы ПП наружной Ø160 SN8, L = 1,0 м</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 18599-2001</t>
+          <t>ГОСТ 32413-2013</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr"/>
       <c r="E52" s="1" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>ввод В1 2,1 м, КХ-8 2,5 м по оси, от 0,15 м за наружной гранью до +0,03 (лист 14, узел 1; ТЗ-1)</t>
+          <t>К1-1 — выпуск (юг) и ввод линии бани (север); баня — выпуски К1-б и К1-бв; К2-1 (лист 14, узел 2)</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПЭ Ø75, 90°, радиус по оси не менее 0,3 м (≥ 8 d трубы в футляре) — гнутый или сварной</t>
+          <t>Футляр из трубы ПЭ 100 SDR17 75×4,5 (техническая) — ввод без приямка: под краем плиты и сквозь плиту, закладывается до бетонирования</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -2008,64 +2008,64 @@
       <c r="E53" s="1" t="inlineStr"/>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
+          <t>ввод В1 2,1 м, КХ-8 2,5 м по оси, от 0,15 м за наружной гранью до +0,03 (лист 14, узел 1; ТЗ-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПЭ Ø75, 90°, радиус по оси не менее 0,3 м (≥ 8 d трубы в футляре) — гнутый или сварной</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>ГОСТ 18599-2001</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
           <t>ввод В1 — 1, КХ-8 — 2; трубу можно вынуть без вскрытия плиты</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>4. Фасонные части (подсчёт по 3D-модели)</t>
         </is>
       </c>
-      <c r="C54" s="1" t="n"/>
-      <c r="D54" s="1" t="n"/>
-      <c r="E54" s="1" t="n"/>
-      <c r="F54" s="1" t="n"/>
-      <c r="G54" s="1" t="n"/>
-      <c r="H54" s="1" t="n"/>
-      <c r="I54" s="1" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>выходы коллекторов</t>
-        </is>
-      </c>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="n"/>
+      <c r="G55" s="1" t="n"/>
+      <c r="H55" s="1" t="n"/>
+      <c r="I55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="G56" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг «евроконус» ¾" для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2151,12 +2151,12 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>выходы коллекторов</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 16×2,2 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2182,12 +2182,12 @@
         </is>
       </c>
       <c r="G59" s="1" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 20×2,8 с переходом на резьбу G½" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2213,12 +2213,12 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>приборы, оборудование, входы коллекторов, КХ</t>
+          <t>приборы, оборудование, входы коллекторов, КХ, Пс (10)</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
+          <t>Фитинг для трубы PE-Xa 25×3,5 с переходом на резьбу G¾" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
+          <t>Фитинг для трубы PE-Xa 32×4,4 с переходом на резьбу G1" (водорозетка, угольник или прямой)</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2275,12 +2275,12 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>ответвления по модели</t>
+          <t>приборы, оборудование, входы коллекторов, КХ</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 16×2,2</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 20×2,8 × 25×3,5</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 20×2,8</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 20×2,8 × 25×3,5</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 20×2,8</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 16×2,2</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Тройник для трубы PE-Xa 25×3,5 × 25×3,5</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 20×2,8</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
+          <t>Тройник для трубы PE-Xa 25×3,5 × 25×3,5</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2461,12 +2461,12 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>выходы из пола</t>
+          <t>ответвления по модели</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 16×2,2</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 20×2,8</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 25×3,5</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
+          <t>Фиксатор поворота 90° для трубы PE-Xa 32×4,4</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2585,12 +2585,12 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>в 1.6 над полом (+0,45), под краном на вводе (лист 7; лист 14, узел 1)</t>
+          <t>выходы из пола</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
+          <t>Переход ПЭ 32 / PE-Xa 32×4,4 (компрессионный или пресс)</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2612,7 +2612,7 @@
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G73" s="1" t="n">
@@ -2621,7 +2621,7 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>в 1.6 над полом (+0,45), под краном на вводе (лист 7; лист 14, узел 1)</t>
         </is>
       </c>
     </row>
@@ -2631,28 +2631,28 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø110, 45°</t>
+          <t>Комплект латунных ниппелей, муфт, американок и уплотнений для сборки водомерного узла Ду 32</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr"/>
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>повороты и низ подъёмов по модели</t>
+          <t>лист 7</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 45°</t>
+          <t>Отвод канализационный малошумный Ø110, 45°</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø50, 30°</t>
+          <t>Отвод канализационный малошумный Ø50, 45°</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 45°</t>
+          <t>Отвод канализационный малошумный Ø50, 30°</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный малошумный Ø32, 30°</t>
+          <t>Отвод канализационный малошумный Ø32, 45°</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
+          <t>Отвод канализационный малошумный Ø32, 30°</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2802,12 +2802,12 @@
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>повороты и низ подъёмов по модели</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Крестовина канализационная малошумная косая 45° Ø50×50×50</t>
+          <t>Тройник канализационный малошумный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2864,12 +2864,12 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>пол 1.4: УМ-1, Д-1, сифон конденсата → Ст.К1-2</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
+          <t>Крестовина канализационная малошумная косая 45° Ø50×50×50</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2900,7 +2900,7 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>пол 1.4: УМ-1, Д-1, сифон конденсата → Ст.К1-2</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 45°</t>
+          <t>Тройник канализационный малошумный косой 45° Ø50×32</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr"/>
@@ -2926,12 +2926,12 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>повороты, низ подъёмов и стояков по модели, прочистки</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø110, 15°</t>
+          <t>Отвод ПП канализационный Ø110, 45°</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2957,12 +2957,12 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>К1-б: поворот 60° в б6 — 45° + 15°</t>
+          <t>повороты, низ подъёмов и стояков по модели, прочистки</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 45°</t>
+          <t>Отвод ПП канализационный Ø110, 15°</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2988,12 +2988,12 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>повороты, низ подъёмов и стояков по модели</t>
+          <t>К1-б: поворот 60° в б6 — 45° + 15°</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП канализационный Ø50, 30°</t>
+          <t>Отвод ПП канализационный Ø50, 45°</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -3019,12 +3019,12 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>К1-М-б1 у стояка</t>
+          <t>повороты, низ подъёмов и стояков по модели</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
+          <t>Отвод ПП канализационный Ø50, 30°</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3050,12 +3050,12 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>К1-М-б1 у стояка</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный 87,5° Ø110×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3081,12 +3081,12 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>на выводе прочистки Ст.К1-2 — отвод Ø50 из пола 1.4</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
+          <t>Тройник ПП канализационный 87,5° Ø110×50</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3112,12 +3112,12 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>присоединения по модели</t>
+          <t>на выводе прочистки Ст.К1-2 — отвод Ø50 из пола 1.4</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×50</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
+          <t>Тройник ПП канализационный косой 45° Ø50×50</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>б6, 1.8, 1.9</t>
+          <t>присоединения по модели</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
+          <t>Тройник ПП канализационный косой 45° Ø110×110 — прочистки в грунте</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3205,12 +3205,12 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
+          <t>б6, 1.8, 1.9</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Ревизия канализационная малошумная Ø110</t>
+          <t>Крестовина ПП канализационная двухплоскостная 87,5° Ø110 с боковыми входами Ø110 и Ø50 (под 90° в плане)</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr"/>
@@ -3236,12 +3236,12 @@
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
+          <t>низ Ст.К1-б: с востока — УН-б1 Ø110, с севера — М-б1 и ГБ Б2 Ø50; ниже — 2 отвода 45°</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
+          <t>Ревизия канализационная малошумная Ø110</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>ГОСТ 32414-2013; в системе малошумных труб</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr"/>
@@ -3272,7 +3272,7 @@
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>прочистки в грунте</t>
+          <t>Ст.К1-1 (+1,000), Ст.К1-б (+0,500), начало сборного в гараже</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
+          <t>Заглушка ПП канализационная Ø110 с уплотнительным кольцом</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3294,46 +3294,62 @@
       <c r="E95" s="1" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>прочистки в грунте</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="inlineStr"/>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="n"/>
-      <c r="D96" s="1" t="n"/>
-      <c r="E96" s="1" t="n"/>
-      <c r="F96" s="1" t="n"/>
-      <c r="G96" s="1" t="n"/>
-      <c r="H96" s="1" t="n"/>
-      <c r="I96" s="1" t="n"/>
+      <c r="A96" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Отвод SML DN100, 45°</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>EN 877; в системе труб SML</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr"/>
+      <c r="E96" s="1" t="inlineStr"/>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H96" s="1" t="inlineStr"/>
+      <c r="I96" s="1" t="inlineStr">
+        <is>
+          <t>низ стояков К2 — по 2 (16), повороты выпусков к ДК-5 и ДК-7 в плане — по 2 (4); лист 15</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
+          <t>Ревизия SML DN100 с крышкой на болтах</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>EN 877; в системе труб SML</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr"/>
@@ -3344,27 +3360,27 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>вход В1 в ШВК-2</t>
+          <t>на каждом стояке Ст.К2-1…8 на +1,000 (лист 15)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
+          <t>Хомут соединительный SML DN100 из нержавеющей стали с уплотнением EPDM и когтевой фиксацией (Kombi, CE или аналог)</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>EN 877; в системе труб SML</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr"/>
@@ -3375,27 +3391,27 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
+          <t>стыки труб и фасонных частей К2: 59 по модели + 10 %; при засоре стояк работает под напором — соединения с фиксацией от сдвига</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
+          <t>Переход SML DN100 / ПП Ø110 (соединительный хомут для пластиковой трубы того же наружного Ø)</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>EN 877; в системе труб SML</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr"/>
@@ -3406,76 +3422,60 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, В1 мойки М-б1 под мойкой, к смесителю Д-б1 (тройник кольца), Т3 кухни бани — у Б2 и к смесителю мойки М-б1 — 2, Т4 кухни бани и кольца ШВК-Б1 у Н9</t>
+          <t>8 — к патрубкам воронок, 8 — на входе в ДК (граница с НВК); лист 15</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ду 15 (Т4)</t>
+          <t>Патрубок компенсационный, переходы, заглушки и уплотнительные кольца ПП Ø32–110</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr"/>
       <c r="E100" s="1" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>на Т4 у Н8, Н9 и на Т4 каждого кольца — рядом с балансировочным клапаном (против противотока)</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr"/>
-      <c r="E101" s="1" t="inlineStr"/>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" s="1" t="inlineStr"/>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>КХ-8, подводка автополива</t>
-        </is>
-      </c>
+      <c r="A101" s="1" t="inlineStr"/>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>5. Арматура (по 3D-модели; краны на выходах коллекторов — в поз. коллекторов: 44 шт.)</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n"/>
+      <c r="D101" s="1" t="n"/>
+      <c r="E101" s="1" t="n"/>
+      <c r="F101" s="1" t="n"/>
+      <c r="G101" s="1" t="n"/>
+      <c r="H101" s="1" t="n"/>
+      <c r="I101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Кран спускной Ду 15 со штуцером</t>
+          <t>Кран шаровой Ду 25, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3504,7 +3504,7 @@
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>КХ-8: слив подводки автополива на зиму</t>
+          <t>вход В1 в ШВК-2</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+          <t>Кран шаровой Ду 20, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -3530,12 +3530,12 @@
         </is>
       </c>
       <c r="G103" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>КХ-8, за наружной гранью фундамента</t>
+          <t>Т3 у Б1, вход Т3 в ШВК-2, Т3 к ШВК-1 в 1.6, вход В1 в ШВК-Б2, вход В1 в ШВК-Б1, Т3 к ШВК-Б1 у Б2</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
+          <t>Кран шаровой Ду 15, PN16, под трубу PE-Xa</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3561,12 +3561,12 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, кухня бани — под мойкой М-б1, ШВК-Б2 (П4)</t>
+          <t>В1 кухни под мойкой, Т4 у Б1 и Н8 — 2, Т3 кухни — в 1.6 и к смесителю мойки — 2, Т4 кухни в 1.6, Т3 у Б2, В1 мойки М-б1 под мойкой, к смесителю Д-б1 (тройник кольца), Т3 кухни бани — у Б2 и к смесителю мойки М-б1 — 2, Т4 кухни бани и кольца ШВК-Б1 у Н9</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
+          <t>Клапан обратный Ду 15 (Т4)</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Arrowhead 485 или аналог</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr"/>
@@ -3592,12 +3592,12 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
+          <t>на Т4 у Н8, Н9 и на Т4 каждого кольца — рядом с балансировочным клапаном (против противотока)</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
+          <t>Клапан обратный пружинный Ду 20 — защита сети от обратного потока</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3628,7 +3628,7 @@
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>КХ-8, подводка автополива</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
+          <t>Кран спускной Ду 15 со штуцером</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3654,184 +3654,184 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>УМ, М — по 2, ПММ — 1</t>
+          <t>КХ-8: слив подводки автополива на зиму</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="inlineStr"/>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>6. Санитарные приборы и изделия канализации</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="n"/>
-      <c r="D108" s="1" t="n"/>
-      <c r="E108" s="1" t="n"/>
-      <c r="F108" s="1" t="n"/>
-      <c r="G108" s="1" t="n"/>
-      <c r="H108" s="1" t="n"/>
-      <c r="I108" s="1" t="n"/>
+      <c r="A108" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Заглушка для трубы PE-Xa 25×3,5 (до подключения автополива)</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr"/>
+      <c r="E108" s="1" t="inlineStr"/>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1" t="inlineStr"/>
+      <c r="I108" s="1" t="inlineStr">
+        <is>
+          <t>КХ-8, за наружной гранью фундамента</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
+          <t>Клапан балансировочный ручной Ду 15 с измерительными ниппелями, Kvs 0,5–1,0</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr"/>
       <c r="E109" s="1" t="inlineStr"/>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
+          <t>на Т4 каждого кольца: кухня — под мойкой М-1, ШВК-2, ШВК-1, кольцо ШВК-Б1 — под мойкой М-б1, кухня бани — под мойкой М-б1, ШВК-Б2 (П4)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Умывальник со смесителем и сифоном</t>
+          <t>Кран поливочный незамерзающий 1/2" ВР × 3/4" НР с вакуумным прерывателем, шток 350 мм через стену</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>Arrowhead 485 или аналог</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr"/>
       <c r="E110" s="1" t="inlineStr"/>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>УМ-1…УМ-4, УМ-б1</t>
+          <t>ПК-1…ПК-3 (решение Заказчицы); слива на зиму не нужно, шланг на зиму снимать</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Ванна со смесителем (душевой системой) и сифоном</t>
+          <t>Кран для стиральной машины Ду 15 с обратным клапаном</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr"/>
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>В-2, В-3, В-б1</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
+          <t>Кран шаровой угловой Ду 15 для гибких подводок (умывальники, мойки, ПММ)</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>по дизайн-проекту</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
       <c r="E112" s="1" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
+          <t>УМ, М — по 2, ПММ — 1</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>по дизайн-проекту</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr"/>
-      <c r="E113" s="1" t="inlineStr"/>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>М-1, М-б1</t>
-        </is>
-      </c>
+      <c r="A113" s="1" t="inlineStr"/>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>6. Санитарные приборы и изделия канализации</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n"/>
+      <c r="D113" s="1" t="n"/>
+      <c r="E113" s="1" t="n"/>
+      <c r="F113" s="1" t="n"/>
+      <c r="G113" s="1" t="n"/>
+      <c r="H113" s="1" t="n"/>
+      <c r="I113" s="1" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Смеситель настенный для наполнения СПА</t>
+          <t>Унитаз подвесной с инсталляцией и кнопкой смыва</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3851,16 +3851,16 @@
       <c r="E114" s="1" t="inlineStr"/>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>СПА (б7)</t>
+          <t>УН-1…УН-3, УН-б1; поставка — по дизайн-проекту</t>
         </is>
       </c>
     </row>
@@ -3870,28 +3870,28 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
+          <t>Умывальник со смесителем и сифоном</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr"/>
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>Д-3, Д-б1</t>
+          <t>УМ-1…УМ-4, УМ-б1</t>
         </is>
       </c>
     </row>
@@ -3901,28 +3901,28 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
+          <t>Ванна со смесителем (душевой системой) и сифоном</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr"/>
       <c r="E116" s="1" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>Т-1 (топочная)</t>
+          <t>В-2, В-3, В-б1</t>
         </is>
       </c>
     </row>
@@ -3932,28 +3932,28 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
+          <t>Душ: душевая система, кабина или трап — по дизайн-проекту</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr"/>
       <c r="E117" s="1" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>Т-б2 (б8)</t>
+          <t>Д-1 (кабина), Д-3, Д-б1 (трап)</t>
         </is>
       </c>
     </row>
@@ -3963,28 +3963,28 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
+          <t>Мойка кухонная со смесителем и сифоном с отводом для ПММ</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr"/>
       <c r="E118" s="1" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>Т-б1 (б7)</t>
+          <t>М-1, М-б1</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
+          <t>Смеситель настенный для наполнения СПА</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по дизайн-проекту</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr"/>
@@ -4010,12 +4010,12 @@
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
+          <t>СПА (б7)</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
+          <t>Трап душевой Ду 50 с сухим затвором (линейный или точечный)</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -4041,12 +4041,12 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>СМ-1</t>
+          <t>Д-3, Д-б1</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
+          <t>Трап Ду 50 с сухим затвором, горизонтальный выпуск</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -4077,7 +4077,7 @@
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>сброс ГБ Б2</t>
+          <t>Т-1 (топочная)</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
+          <t>Трап Ду 50 с сухим затвором, вертикальный выпуск, термостойкий (для парной)</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -4108,7 +4108,7 @@
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
+          <t>Т-б2 (б8)</t>
         </is>
       </c>
     </row>
@@ -4118,12 +4118,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
+          <t>Трап Ду 100 с сухим затвором, вертикальный выпуск</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>по системе кровли</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr"/>
@@ -4134,12 +4134,12 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>Ст.К1-1в, Ст.К1-б</t>
+          <t>Т-б1 (б7)</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
+          <t>Сифон для конденсата кондиционеров с сухим затвором, встраиваемый в стену, с ревизией</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -4165,12 +4165,12 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
+          <t>1.4, 2.9 — 2 шт. (лист 14, узел 7)</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
+          <t>Сифон встраиваемый для стиральной машины с обратным клапаном</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -4192,16 +4192,16 @@
       <c r="E125" s="1" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
+          <t>СМ-1</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
+          <t>Воронка с разрывом струи и сухим затвором Ду 32/50</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -4232,37 +4232,53 @@
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>ПУ-1, гараж (лист 4)</t>
+          <t>сброс ГБ Б2</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="inlineStr"/>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="n"/>
-      <c r="D127" s="1" t="n"/>
-      <c r="E127" s="1" t="n"/>
-      <c r="F127" s="1" t="n"/>
-      <c r="G127" s="1" t="n"/>
-      <c r="H127" s="1" t="n"/>
-      <c r="I127" s="1" t="n"/>
+      <c r="A127" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Сифон Ø50 для слива СПА с гидрозатвором, ревизией и присоединением гибкого шланга через шаровой кран</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr"/>
+      <c r="E127" s="1" t="inlineStr"/>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="1" t="inlineStr"/>
+      <c r="I127" s="1" t="inlineStr">
+        <is>
+          <t>К1-СПА — выпуск из пола у северного борта СПА (б7); место — по паспорту СПА</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
+          <t>Элемент кровельный проходной для канализационного стояка Ø110 с хомутом</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Neptun, Аквасторож, или аналог</t>
+          <t>по системе кровли</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr"/>
@@ -4278,17 +4294,17 @@
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
+          <t>Ст.К1-1в, Ст.К1-б</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
+          <t>Люк ревизионный нажимной 300×400 мм под плитку или окраску (в стене)</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -4304,22 +4320,22 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>КЭ-1 — ввод после водомерного узла</t>
+          <t>прочистки (б6, 1.8, 1.9), ревизии Ст.К1-1 и Ст.К1-б (лист 14, узел 5)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
+          <t>Лоток водоотводный пластиковый DN100 с решёткой класса нагрузки C250 и торцевыми заглушками</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4331,31 +4347,31 @@
       <c r="E130" s="1" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
+          <t>ЛГ-1, гараж, вдоль ворот (L ≈ 6,1 м)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Датчик протечки проводной напольный</t>
+          <t>Пескоуловитель DN100 с корзиной и решёткой C250, вертикальный выпуск Ø110</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr"/>
@@ -4366,130 +4382,130 @@
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>ДП-1…ДП-19</t>
+          <t>ПУ-1, гараж (лист 4)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Кабель-удлинитель датчиков (системный)</t>
+          <t>Кровельная воронка Ø110 с вертикальным выпуском и листвоуловителем; тип, обогрев и фланец под кровельный материал — по АР</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>той же системы</t>
+          <t>HL62.1 / HL64.1H (в модели АР) или аналог</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr"/>
       <c r="E132" s="1" t="inlineStr"/>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>оценка по плану; прокладка — ЭОМ/СС</t>
+          <t>Вр-1…Вр-5 — кровля над 2 этажом (АР14), Вр-6…Вр-8 — кровли над 1 этажом (АР13.1); лист 15</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="inlineStr"/>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>8. Изоляция, гильзы и крепления</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="n"/>
-      <c r="D133" s="1" t="n"/>
-      <c r="E133" s="1" t="n"/>
-      <c r="F133" s="1" t="n"/>
-      <c r="G133" s="1" t="n"/>
-      <c r="H133" s="1" t="n"/>
-      <c r="I133" s="1" t="n"/>
+      <c r="A133" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Люк нажимной ревизионный 300×300 мм под отделку (в стене, у ревизии водостока)</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr"/>
+      <c r="E133" s="1" t="inlineStr"/>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H133" s="1" t="inlineStr"/>
+      <c r="I133" s="1" t="inlineStr">
+        <is>
+          <t>ревизии Ст.К2: люки со стороны 1.3, 1.5 (2), 1.9, 1.10, 1.11 (2), 1.12; у Ст.К2-8 — на террасе 1.12, для наружной установки (лист 15; ТЗ-1)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr"/>
-      <c r="E134" s="1" t="inlineStr"/>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H134" s="1" t="inlineStr"/>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="A134" s="1" t="inlineStr"/>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>7. Защита от протечек (опросный лист: мокрые зоны)</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n"/>
+      <c r="D134" s="1" t="n"/>
+      <c r="E134" s="1" t="n"/>
+      <c r="F134" s="1" t="n"/>
+      <c r="G134" s="1" t="n"/>
+      <c r="H134" s="1" t="n"/>
+      <c r="I134" s="1" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
+          <t>Контроллер системы защиты от протечек на 2 крана с электроприводом, выход «авария» (сухой контакт) для умного дома, питание 230 В</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Neptun, Аквасторож, или аналог</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr"/>
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>154</v>
+        <v>2</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЗП-1 (1.6), КЗП-2 (б4)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
+          <t>Кран шаровой Ду 32 с электроприводом, 12 В, латунь, время закрытия не более 30 с</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4501,26 +4517,26 @@
       <c r="E136" s="1" t="inlineStr"/>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G136" s="1" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЭ-1 — ввод после водомерного узла</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
+          <t>Кран шаровой Ду 20 с электроприводом, 12 В, латунь</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4532,62 +4548,62 @@
       <c r="E137" s="1" t="inlineStr"/>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>КЭ-2 — вход В1 в ШВК-Б2, КЭ-3 — вход В1 в ШВК-Б1 (баня, КЗП-2)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
+          <t>Датчик протечки проводной напольный</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr"/>
       <c r="E138" s="1" t="inlineStr"/>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>ДП-1…ДП-19</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
+          <t>Кабель-удлинитель датчиков (системный)</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>той же системы</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr"/>
@@ -4598,45 +4614,29 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
+          <t>оценка по плану; прокладка — ЭОМ/СС</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="inlineStr"/>
-      <c r="E140" s="1" t="inlineStr"/>
-      <c r="F140" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G140" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="H140" s="1" t="inlineStr"/>
-      <c r="I140" s="1" t="inlineStr">
-        <is>
-          <t>λ ≤ 0,038 Вт/(м·°С)</t>
-        </is>
-      </c>
+      <c r="A140" s="1" t="inlineStr"/>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>8. Изоляция, гильзы и крепления</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n"/>
+      <c r="D140" s="1" t="n"/>
+      <c r="E140" s="1" t="n"/>
+      <c r="F140" s="1" t="n"/>
+      <c r="G140" s="1" t="n"/>
+      <c r="H140" s="1" t="n"/>
+      <c r="I140" s="1" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×13 мм (Т3, Т4, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4660,12 +4660,12 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×13 мм (Т3, Т4, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -4691,12 +4691,12 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>39</v>
+        <v>154</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>подъёмы к приборам</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4706,28 +4706,28 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×13 мм (Т3, Т4, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr"/>
       <c r="E143" s="1" t="inlineStr"/>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4737,28 +4737,28 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø18×9 мм (В1, PE-Xa 16×2,2)</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr"/>
       <c r="E144" s="1" t="inlineStr"/>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 17, стены 9 (ТЗ-1, лист 4; лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4768,28 +4768,28 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø22×9 мм (В1, PE-Xa 20×2,8)</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 32414-2013</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr"/>
       <c r="E145" s="1" t="inlineStr"/>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>плиты и перекрытия 15, стены 0 (ТЗ-1, лист 4; лист 14)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø28×9 мм (В1, PE-Xa 25×3,5)</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -4811,16 +4811,16 @@
       <c r="E146" s="1" t="inlineStr"/>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>п. 11.5; лист 14</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø35×9 мм (В1, PE-Xa 32×4,4)</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -4842,16 +4842,16 @@
       <c r="E147" s="1" t="inlineStr"/>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
+          <t>λ ≤ 0,038 Вт/(м·°С)</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
+          <t>Труба гофрированная защитная ПНД Ø40 — В1 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -4873,16 +4873,16 @@
       <c r="E148" s="1" t="inlineStr"/>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>3 проёма (ТЗ-1, лист 4)</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
+          <t>Труба гофрированная защитная ПНД Ø50 — Т3, Т4 в изоляции, в стенах</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -4904,16 +4904,16 @@
       <c r="E149" s="1" t="inlineStr"/>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G149" s="1" t="n">
-        <v>2.4</v>
+        <v>39</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr">
         <is>
-          <t>лист 6; НВК — так же во дворе</t>
+          <t>подъёмы к приборам</t>
         </is>
       </c>
     </row>
@@ -4923,28 +4923,28 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
+          <t>Гильза из трубы ПП Ø50, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr"/>
       <c r="E150" s="1" t="inlineStr"/>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr">
         <is>
-          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
+          <t>плиты и перекрытия 0, стены 8 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø75, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr"/>
@@ -4970,12 +4970,12 @@
         </is>
       </c>
       <c r="G151" s="1" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 17, стены 9 (ТЗ-1, лист 4; лист 14)</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+          <t>Гильза из трубы ПП Ø160, L = толщина конструкции</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 32414-2013</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr"/>
@@ -5001,12 +5001,12 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>плиты и перекрытия 28, стены 8 (ТЗ-1, лист 4; лист 14; в т. ч. водостоки К2 — 21, лист 15)</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+          <t>Заделка гильз: негорючий гидрофобный материал / огнезащитный герметик</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -5028,16 +5028,16 @@
       <c r="E153" s="1" t="inlineStr"/>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>п. 11.5; лист 14</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+          <t>Заделка торцов футляров: уплотнитель из вспененного полиэтилена и герметик полиуретановый</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -5059,16 +5059,16 @@
       <c r="E154" s="1" t="inlineStr"/>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G154" s="1" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>футляры Ø75 ввода В1 и КХ-8, футляры Ø160 К1-1 (юг, север), К1-б, К1-бв, К2-1 (п. 8.8)</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+          <t>Заделка проёмов под пучки труб в плитах и стенах — тем же материалом вокруг каждой трубы</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -5090,16 +5090,16 @@
       <c r="E155" s="1" t="inlineStr"/>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>3 проёма (ТЗ-1, лист 4)</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+          <t>Плита ЭППС 50 мм (утепление К1-1 под неотапливаемой террасой 1.13, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -5121,16 +5121,16 @@
       <c r="E156" s="1" t="inlineStr"/>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G156" s="1" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>лист 6; НВК — так же во дворе</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+          <t>Плита ЭППС 50 мм (утепление К1-б под неотапливаемой террасой бани б1, ширина 1,2 м)</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -5152,16 +5152,16 @@
       <c r="E157" s="1" t="inlineStr"/>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G157" s="1" t="n">
-        <v>48</v>
+        <v>3.1</v>
       </c>
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr">
         <is>
-          <t>шаг — лист 14</t>
+          <t>лист 9; от стеклянной стены б6 до края плиты 2,3 м (ТЗ-1)</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена Ø114×9 мм (К2, SML DN100 — от конденсата)</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -5183,139 +5183,466 @@
       <c r="E158" s="1" t="inlineStr"/>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G158" s="1" t="n">
-        <v>650</v>
+        <v>60</v>
       </c>
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="1" t="inlineStr">
         <is>
-          <t>шаг 0,5 м</t>
+          <t>стояки и выпуски К2 в стенах дома, кроме Ст.К2-8 в стене террасы 1.12; у хомутов — встык</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="inlineStr"/>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>9. Не входит в ВК.СО</t>
-        </is>
-      </c>
-      <c r="C159" s="1" t="n"/>
-      <c r="D159" s="1" t="n"/>
-      <c r="E159" s="1" t="n"/>
-      <c r="F159" s="1" t="n"/>
-      <c r="G159" s="1" t="n"/>
-      <c r="H159" s="1" t="n"/>
-      <c r="I159" s="1" t="n"/>
+      <c r="A159" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 16×2,2, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr"/>
+      <c r="E159" s="1" t="inlineStr"/>
+      <c r="F159" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="H159" s="1" t="inlineStr"/>
+      <c r="I159" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
-        </is>
-      </c>
-      <c r="C160" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 20×2,8, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D160" s="1" t="inlineStr"/>
       <c r="E160" s="1" t="inlineStr"/>
-      <c r="F160" s="1" t="inlineStr"/>
-      <c r="G160" s="1" t="inlineStr"/>
+      <c r="F160" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>83</v>
+      </c>
       <c r="H160" s="1" t="inlineStr"/>
-      <c r="I160" s="1" t="inlineStr"/>
+      <c r="I160" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
-        </is>
-      </c>
-      <c r="C161" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 25×3,5, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D161" s="1" t="inlineStr"/>
       <c r="E161" s="1" t="inlineStr"/>
-      <c r="F161" s="1" t="inlineStr"/>
-      <c r="G161" s="1" t="inlineStr"/>
+      <c r="F161" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>89</v>
+      </c>
       <c r="H161" s="1" t="inlineStr"/>
-      <c r="I161" s="1" t="inlineStr"/>
+      <c r="I161" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
-        </is>
-      </c>
-      <c r="C162" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для PE-Xa 32×4,4, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D162" s="1" t="inlineStr"/>
       <c r="E162" s="1" t="inlineStr"/>
-      <c r="F162" s="1" t="inlineStr"/>
-      <c r="G162" s="1" t="inlineStr"/>
+      <c r="F162" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G162" s="1" t="n">
+        <v>24</v>
+      </c>
       <c r="H162" s="1" t="inlineStr"/>
-      <c r="I162" s="1" t="inlineStr"/>
+      <c r="I162" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
-        </is>
-      </c>
-      <c r="C163" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø110, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D163" s="1" t="inlineStr"/>
       <c r="E163" s="1" t="inlineStr"/>
-      <c r="F163" s="1" t="inlineStr"/>
-      <c r="G163" s="1" t="inlineStr"/>
+      <c r="F163" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>26</v>
+      </c>
       <c r="H163" s="1" t="inlineStr"/>
-      <c r="I163" s="1" t="inlineStr"/>
+      <c r="I163" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
-        </is>
-      </c>
-      <c r="C164" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø32, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D164" s="1" t="inlineStr"/>
       <c r="E164" s="1" t="inlineStr"/>
-      <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr"/>
+      <c r="F164" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G164" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="H164" s="1" t="inlineStr"/>
-      <c r="I164" s="1" t="inlineStr"/>
+      <c r="I164" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
-        </is>
-      </c>
-      <c r="C165" s="1" t="inlineStr"/>
+          <t>Хомут трубный с резиновым вкладышем для ПП Ø50, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D165" s="1" t="inlineStr"/>
       <c r="E165" s="1" t="inlineStr"/>
-      <c r="F165" s="1" t="inlineStr"/>
-      <c r="G165" s="1" t="inlineStr"/>
+      <c r="F165" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G165" s="1" t="n">
+        <v>48</v>
+      </c>
       <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr"/>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t>шаг — лист 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Хомут крепёжный SML DN100 с резиновым вкладышем, со шпилькой и анкером</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>в системе труб SML</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr"/>
+      <c r="E166" s="1" t="inlineStr"/>
+      <c r="F166" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G166" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="H166" s="1" t="inlineStr"/>
+      <c r="I166" s="1" t="inlineStr">
+        <is>
+          <t>стояки К2: не реже чем через 2 м и у отводов (лист 15)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" t="inlineStr">
+      <c r="A167" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Опора стояка SML DN100</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>в системе труб SML</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr"/>
+      <c r="E167" s="1" t="inlineStr"/>
+      <c r="F167" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G167" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H167" s="1" t="inlineStr"/>
+      <c r="I167" s="1" t="inlineStr">
+        <is>
+          <t>у основания каждого стояка К2, над отводами</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Скоба-гарпун (фиксатор) для крепления PE-Xa к утеплителю пола</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr"/>
+      <c r="E168" s="1" t="inlineStr"/>
+      <c r="F168" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G168" s="1" t="n">
+        <v>650</v>
+      </c>
+      <c r="H168" s="1" t="inlineStr"/>
+      <c r="I168" s="1" t="inlineStr">
+        <is>
+          <t>шаг 0,5 м</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr"/>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>9. Не входит в ВК.СО</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="n"/>
+      <c r="D169" s="1" t="n"/>
+      <c r="E169" s="1" t="n"/>
+      <c r="F169" s="1" t="n"/>
+      <c r="G169" s="1" t="n"/>
+      <c r="H169" s="1" t="n"/>
+      <c r="I169" s="1" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Бойлеры Б1 300 л и Б2 200 л, санитарная труба Ecoflex Quattro (ввод В1 в баню) — И05.09.26-ОВ.СО</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr"/>
+      <c r="D170" s="1" t="inlineStr"/>
+      <c r="E170" s="1" t="inlineStr"/>
+      <c r="F170" s="1" t="inlineStr"/>
+      <c r="G170" s="1" t="inlineStr"/>
+      <c r="H170" s="1" t="inlineStr"/>
+      <c r="I170" s="1" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>ГБ-ГВС и РБ-ГВС бойлера Б1, нейтрализатор конденсата котлов, подпитка — И05.09.26-ТМ.СО</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr"/>
+      <c r="D171" s="1" t="inlineStr"/>
+      <c r="E171" s="1" t="inlineStr"/>
+      <c r="F171" s="1" t="inlineStr"/>
+      <c r="G171" s="1" t="inlineStr"/>
+      <c r="H171" s="1" t="inlineStr"/>
+      <c r="I171" s="1" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Наружные сети, подключение к поселковым сетям ВК и КК (ДК5-018) — раздел НВК (И05.09.26-НВК)</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr"/>
+      <c r="D172" s="1" t="inlineStr"/>
+      <c r="E172" s="1" t="inlineStr"/>
+      <c r="F172" s="1" t="inlineStr"/>
+      <c r="G172" s="1" t="inlineStr"/>
+      <c r="H172" s="1" t="inlineStr"/>
+      <c r="I172" s="1" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Система автополива участка и водопровод беседки — по ландшафтному проекту и НВК</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr"/>
+      <c r="D173" s="1" t="inlineStr"/>
+      <c r="E173" s="1" t="inlineStr"/>
+      <c r="F173" s="1" t="inlineStr"/>
+      <c r="G173" s="1" t="inlineStr"/>
+      <c r="H173" s="1" t="inlineStr"/>
+      <c r="I173" s="1" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Дождеприёмники ДК-1…ДК-8 300×300 у стен дома, пластиковые трубы К2 после них, ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr"/>
+      <c r="D174" s="1" t="inlineStr"/>
+      <c r="E174" s="1" t="inlineStr"/>
+      <c r="F174" s="1" t="inlineStr"/>
+      <c r="G174" s="1" t="inlineStr"/>
+      <c r="H174" s="1" t="inlineStr"/>
+      <c r="I174" s="1" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Примыкание кровельных воронок к кровле — АР; электропитание обогрева воронок (если обогрев принят в АР) — ЭОМ</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr"/>
+      <c r="D175" s="1" t="inlineStr"/>
+      <c r="E175" s="1" t="inlineStr"/>
+      <c r="F175" s="1" t="inlineStr"/>
+      <c r="G175" s="1" t="inlineStr"/>
+      <c r="H175" s="1" t="inlineStr"/>
+      <c r="I175" s="1" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr"/>
+      <c r="D176" s="1" t="inlineStr"/>
+      <c r="E176" s="1" t="inlineStr"/>
+      <c r="F176" s="1" t="inlineStr"/>
+      <c r="G176" s="1" t="inlineStr"/>
+      <c r="H176" s="1" t="inlineStr"/>
+      <c r="I176" s="1" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-vk/И05.09.26-ВК.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Дождеприёмники ДК-1…ДК-8 300×300 у стен дома, пластиковые трубы К2 после них, ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
+          <t>Дождеприёмники ДК-1…ДК-8 у стен дома и ДК-б1, ДК-б2 у бани, пластиковые трубы К2 после них, ливневая сеть и дренаж участка, приём выпуска лотка гаража К2-1 — раздел НВК</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr"/>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+          <t>Наружные водостоки бани (жёлоб северного карниза, воронки, трубы Ø100 по фасаду) — АР бани (АР14)</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr"/>
@@ -5640,9 +5640,26 @@
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr"/>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr"/>
-      <c r="B178" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Ниши коллекторных шкафов, газобетонные О-блоки с отверстием Ø160 под стояки и выводы прочисток (баня — перегородки б2/б3 и б6/б8 толщиной 250 мм), короб гаража с люком 600×600, короб инсталляции УН-б1 — по АР (ТЗ-1)</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr"/>
+      <c r="D177" s="1" t="inlineStr"/>
+      <c r="E177" s="1" t="inlineStr"/>
+      <c r="F177" s="1" t="inlineStr"/>
+      <c r="G177" s="1" t="inlineStr"/>
+      <c r="H177" s="1" t="inlineStr"/>
+      <c r="I177" s="1" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>
